--- a/xlsx/contratos/latest.xlsx
+++ b/xlsx/contratos/latest.xlsx
@@ -2895,7 +2895,7 @@
     <t>R$ 67698.84</t>
   </si>
   <si>
-    <t>17/12/2026</t>
+    <t>18/02/2027</t>
   </si>
   <si>
     <t>1023 - Thiago Degola - 25/09/26</t>

--- a/xlsx/contratos/latest.xlsx
+++ b/xlsx/contratos/latest.xlsx
@@ -222,7 +222,7 @@
     <t>ANA FREDA IOSIF FUKS</t>
   </si>
   <si>
-    <t>BIANCA RODRIGUES</t>
+    <t>bianca rodrigues</t>
   </si>
   <si>
     <t>Carina Pereira</t>
@@ -13775,7 +13775,7 @@
         <v>69</v>
       </c>
       <c r="F290" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G290" t="s">
         <v>987</v>

--- a/xlsx/contratos/latest.xlsx
+++ b/xlsx/contratos/latest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4046" uniqueCount="1405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4046" uniqueCount="1406">
   <si>
     <t>Contrato</t>
   </si>
@@ -2967,73 +2967,76 @@
     <t>16/10/2026</t>
   </si>
   <si>
+    <t>1051 - Claudio Wasserman - 17/10/26</t>
+  </si>
+  <si>
+    <t>Claudio Wasserman</t>
+  </si>
+  <si>
+    <t>R$ 50900.00</t>
+  </si>
+  <si>
+    <t>17/12/2026</t>
+  </si>
+  <si>
+    <t>1044 - MO REGINA RURIKO - 14/10/26</t>
+  </si>
+  <si>
+    <t>REGINA RURIKO TATEIGI</t>
+  </si>
+  <si>
+    <t>R$ 29700.00</t>
+  </si>
+  <si>
+    <t>19/10/2026</t>
+  </si>
+  <si>
+    <t>1023 - Thiago Degola - 25/09/26</t>
+  </si>
+  <si>
+    <t>Thiago Souza Dias Degola</t>
+  </si>
+  <si>
+    <t>1029 - CARLA EMÍLIA DE OLIVEIRA SOUZA FERREIRA - 01/10/26</t>
+  </si>
+  <si>
+    <t>CARLA EMÍLIA DE OLIVEIRA SOUZA FERREIRA</t>
+  </si>
+  <si>
+    <t>R$ 178.08</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t>15/12/2026</t>
+  </si>
+  <si>
+    <t>1009 - Mariana Andrade Derossi - 17/09/26</t>
+  </si>
+  <si>
+    <t>Mariana Andrade Derossi</t>
+  </si>
+  <si>
+    <t>R$ 67698.84</t>
+  </si>
+  <si>
+    <t>18/02/2027</t>
+  </si>
+  <si>
+    <t>1048 - Venda Avulsa - VIVIAN MOURA BENIFICA GAZOLA</t>
+  </si>
+  <si>
+    <t>VIVIAN MOURA BENIFICA GAZOLA</t>
+  </si>
+  <si>
+    <t>R$ 340.52</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
     <t>23/12/2026</t>
-  </si>
-  <si>
-    <t>1051 - Claudio Wasserman - 17/10/26</t>
-  </si>
-  <si>
-    <t>Claudio Wasserman</t>
-  </si>
-  <si>
-    <t>R$ 50900.00</t>
-  </si>
-  <si>
-    <t>1044 - MO REGINA RURIKO - 14/10/26</t>
-  </si>
-  <si>
-    <t>REGINA RURIKO TATEIGI</t>
-  </si>
-  <si>
-    <t>R$ 29700.00</t>
-  </si>
-  <si>
-    <t>19/10/2026</t>
-  </si>
-  <si>
-    <t>1023 - Thiago Degola - 25/09/26</t>
-  </si>
-  <si>
-    <t>Thiago Souza Dias Degola</t>
-  </si>
-  <si>
-    <t>1029 - CARLA EMÍLIA DE OLIVEIRA SOUZA FERREIRA - 01/10/26</t>
-  </si>
-  <si>
-    <t>CARLA EMÍLIA DE OLIVEIRA SOUZA FERREIRA</t>
-  </si>
-  <si>
-    <t>R$ 178.08</t>
-  </si>
-  <si>
-    <t>07/10/2026</t>
-  </si>
-  <si>
-    <t>15/12/2026</t>
-  </si>
-  <si>
-    <t>1009 - Mariana Andrade Derossi - 17/09/26</t>
-  </si>
-  <si>
-    <t>Mariana Andrade Derossi</t>
-  </si>
-  <si>
-    <t>R$ 67698.84</t>
-  </si>
-  <si>
-    <t>18/02/2027</t>
-  </si>
-  <si>
-    <t>1048 - Venda Avulsa - VIVIAN MOURA BENIFICA GAZOLA</t>
-  </si>
-  <si>
-    <t>VIVIAN MOURA BENIFICA GAZOLA</t>
-  </si>
-  <si>
-    <t>R$ 340.52</t>
-  </si>
-  <si>
-    <t>15/10/2026</t>
   </si>
   <si>
     <t>1047 - Patrícia Santos da Silva - 15/10/26</t>
@@ -13717,7 +13720,7 @@
         <v>983</v>
       </c>
       <c r="J288" t="s">
-        <v>984</v>
+        <v>957</v>
       </c>
       <c r="K288" t="s">
         <v>2</v>
@@ -13763,10 +13766,10 @@
         <v>105101.0</v>
       </c>
       <c r="B290" t="s">
+        <v>984</v>
+      </c>
+      <c r="C290" t="s">
         <v>985</v>
-      </c>
-      <c r="C290" t="s">
-        <v>986</v>
       </c>
       <c r="D290" t="s">
         <v>69</v>
@@ -13778,7 +13781,7 @@
         <v>52</v>
       </c>
       <c r="G290" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H290" t="s">
         <v>38</v>
@@ -13787,7 +13790,7 @@
         <v>915</v>
       </c>
       <c r="J290" t="s">
-        <v>98</v>
+        <v>987</v>
       </c>
       <c r="K290" t="s">
         <v>2</v>
@@ -13962,7 +13965,7 @@
         <v>1006</v>
       </c>
       <c r="J295" t="s">
-        <v>984</v>
+        <v>1007</v>
       </c>
       <c r="K295" t="s">
         <v>2</v>
@@ -13973,7 +13976,7 @@
         <v>104701.0</v>
       </c>
       <c r="B296" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C296" t="s">
         <v>795</v>
@@ -13988,7 +13991,7 @@
         <v>45</v>
       </c>
       <c r="G296" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H296" t="s">
         <v>38</v>
@@ -13997,7 +14000,7 @@
         <v>1006</v>
       </c>
       <c r="J296" t="s">
-        <v>984</v>
+        <v>1007</v>
       </c>
       <c r="K296" t="s">
         <v>2</v>
@@ -14008,7 +14011,7 @@
         <v>103501.0</v>
       </c>
       <c r="B297" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C297" t="s">
         <v>597</v>
@@ -14023,7 +14026,7 @@
         <v>45</v>
       </c>
       <c r="G297" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H297" t="s">
         <v>38</v>
@@ -14043,10 +14046,10 @@
         <v>103801.0</v>
       </c>
       <c r="B298" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C298" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D298" t="s">
         <v>146</v>
@@ -14058,7 +14061,7 @@
         <v>45</v>
       </c>
       <c r="G298" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H298" t="s">
         <v>38</v>
@@ -14067,7 +14070,7 @@
         <v>1006</v>
       </c>
       <c r="J298" t="s">
-        <v>984</v>
+        <v>1007</v>
       </c>
       <c r="K298" t="s">
         <v>2</v>
@@ -14078,10 +14081,10 @@
         <v>92901.0</v>
       </c>
       <c r="B299" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C299" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D299" t="s">
         <v>69</v>
@@ -14093,7 +14096,7 @@
         <v>45</v>
       </c>
       <c r="G299" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H299" t="s">
         <v>38</v>
@@ -14113,10 +14116,10 @@
         <v>95301.0</v>
       </c>
       <c r="B300" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C300" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D300" t="s">
         <v>159</v>
@@ -14128,16 +14131,16 @@
         <v>45</v>
       </c>
       <c r="G300" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H300" t="s">
         <v>38</v>
       </c>
       <c r="I300" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="J300" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="K300" t="s">
         <v>2</v>
@@ -14148,10 +14151,10 @@
         <v>95001.0</v>
       </c>
       <c r="B301" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C301" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D301" t="s">
         <v>43</v>
@@ -14169,7 +14172,7 @@
         <v>47</v>
       </c>
       <c r="I301" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="J301" t="s">
         <v>49</v>
@@ -14183,10 +14186,10 @@
         <v>94401.0</v>
       </c>
       <c r="B302" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C302" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D302" t="s">
         <v>69</v>
@@ -14204,7 +14207,7 @@
         <v>38</v>
       </c>
       <c r="I302" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="J302" t="s">
         <v>957</v>
@@ -14218,7 +14221,7 @@
         <v>96401.0</v>
       </c>
       <c r="B303" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C303" t="s">
         <v>765</v>
@@ -14233,16 +14236,16 @@
         <v>45</v>
       </c>
       <c r="G303" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H303" t="s">
         <v>38</v>
       </c>
       <c r="I303" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="J303" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="K303" t="s">
         <v>2</v>
@@ -14253,7 +14256,7 @@
         <v>96801.0</v>
       </c>
       <c r="B304" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C304" t="s">
         <v>96</v>
@@ -14268,16 +14271,16 @@
         <v>45</v>
       </c>
       <c r="G304" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H304" t="s">
         <v>38</v>
       </c>
       <c r="I304" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="J304" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="K304" t="s">
         <v>2</v>
@@ -14288,7 +14291,7 @@
         <v>97301.0</v>
       </c>
       <c r="B305" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C305" t="s">
         <v>838</v>
@@ -14303,7 +14306,7 @@
         <v>45</v>
       </c>
       <c r="G305" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H305" t="s">
         <v>38</v>
@@ -14312,7 +14315,7 @@
         <v>859</v>
       </c>
       <c r="J305" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="K305" t="s">
         <v>2</v>
@@ -14323,7 +14326,7 @@
         <v>94301.0</v>
       </c>
       <c r="B306" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C306" t="s">
         <v>861</v>
@@ -14344,10 +14347,10 @@
         <v>38</v>
       </c>
       <c r="I306" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="J306" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="K306" t="s">
         <v>2</v>
@@ -14358,10 +14361,10 @@
         <v>93701.0</v>
       </c>
       <c r="B307" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C307" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D307" t="s">
         <v>69</v>
@@ -14373,7 +14376,7 @@
         <v>45</v>
       </c>
       <c r="G307" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H307" t="s">
         <v>38</v>
@@ -14393,10 +14396,10 @@
         <v>91901.0</v>
       </c>
       <c r="B308" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C308" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D308" t="s">
         <v>69</v>
@@ -14408,7 +14411,7 @@
         <v>52</v>
       </c>
       <c r="G308" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H308" t="s">
         <v>47</v>
@@ -14428,10 +14431,10 @@
         <v>92301.0</v>
       </c>
       <c r="B309" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C309" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D309" t="s">
         <v>69</v>
@@ -14449,7 +14452,7 @@
         <v>38</v>
       </c>
       <c r="I309" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="J309" t="s">
         <v>586</v>
@@ -14463,7 +14466,7 @@
         <v>93401.0</v>
       </c>
       <c r="B310" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="C310" t="s">
         <v>869</v>
@@ -14478,16 +14481,16 @@
         <v>45</v>
       </c>
       <c r="G310" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H310" t="s">
         <v>38</v>
       </c>
       <c r="I310" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="J310" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="K310" t="s">
         <v>2</v>
@@ -14533,7 +14536,7 @@
         <v>95701.0</v>
       </c>
       <c r="B312" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C312" t="s">
         <v>191</v>
@@ -14548,16 +14551,16 @@
         <v>45</v>
       </c>
       <c r="G312" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H312" t="s">
         <v>38</v>
       </c>
       <c r="I312" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="J312" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="K312" t="s">
         <v>2</v>
@@ -14568,10 +14571,10 @@
         <v>98701.0</v>
       </c>
       <c r="B313" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C313" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D313" t="s">
         <v>839</v>
@@ -14589,7 +14592,7 @@
         <v>38</v>
       </c>
       <c r="I313" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="J313" t="s">
         <v>788</v>
@@ -14603,7 +14606,7 @@
         <v>99401.0</v>
       </c>
       <c r="B314" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C314" t="s">
         <v>829</v>
@@ -14624,10 +14627,10 @@
         <v>38</v>
       </c>
       <c r="I314" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="J314" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="K314" t="s">
         <v>2</v>
@@ -14638,10 +14641,10 @@
         <v>95401.0</v>
       </c>
       <c r="B315" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C315" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D315" t="s">
         <v>839</v>
@@ -14653,13 +14656,13 @@
         <v>45</v>
       </c>
       <c r="G315" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H315" t="s">
         <v>38</v>
       </c>
       <c r="I315" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="J315" t="s">
         <v>586</v>
@@ -14673,7 +14676,7 @@
         <v>96901.0</v>
       </c>
       <c r="B316" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C316" t="s">
         <v>305</v>
@@ -14688,13 +14691,13 @@
         <v>45</v>
       </c>
       <c r="G316" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H316" t="s">
         <v>38</v>
       </c>
       <c r="I316" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="J316" t="s">
         <v>586</v>
@@ -14708,10 +14711,10 @@
         <v>96101.0</v>
       </c>
       <c r="B317" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C317" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D317" t="s">
         <v>839</v>
@@ -14723,7 +14726,7 @@
         <v>45</v>
       </c>
       <c r="G317" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H317" t="s">
         <v>38</v>
@@ -14743,10 +14746,10 @@
         <v>96501.0</v>
       </c>
       <c r="B318" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C318" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="D318" t="s">
         <v>35</v>
@@ -14758,16 +14761,16 @@
         <v>52</v>
       </c>
       <c r="G318" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H318" t="s">
         <v>38</v>
       </c>
       <c r="I318" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="J318" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="K318" t="s">
         <v>2</v>
@@ -14778,10 +14781,10 @@
         <v>94901.0</v>
       </c>
       <c r="B319" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C319" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D319" t="s">
         <v>35</v>
@@ -14793,16 +14796,16 @@
         <v>45</v>
       </c>
       <c r="G319" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H319" t="s">
         <v>38</v>
       </c>
       <c r="I319" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="J319" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="K319" t="s">
         <v>2</v>
@@ -14813,10 +14816,10 @@
         <v>56102.0</v>
       </c>
       <c r="B320" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C320" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D320" t="s">
         <v>35</v>
@@ -14828,13 +14831,13 @@
         <v>45</v>
       </c>
       <c r="G320" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H320" t="s">
         <v>38</v>
       </c>
       <c r="I320" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="J320" t="s">
         <v>788</v>
@@ -14869,10 +14872,10 @@
         <v>38</v>
       </c>
       <c r="I321" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="J321" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="K321" t="s">
         <v>2</v>
@@ -14883,10 +14886,10 @@
         <v>97401.0</v>
       </c>
       <c r="B322" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C322" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D322" t="s">
         <v>35</v>
@@ -14898,16 +14901,16 @@
         <v>45</v>
       </c>
       <c r="G322" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H322" t="s">
         <v>38</v>
       </c>
       <c r="I322" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="J322" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="K322" t="s">
         <v>2</v>
@@ -14918,10 +14921,10 @@
         <v>97601.0</v>
       </c>
       <c r="B323" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C323" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="D323" t="s">
         <v>839</v>
@@ -14933,13 +14936,13 @@
         <v>45</v>
       </c>
       <c r="G323" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H323" t="s">
         <v>38</v>
       </c>
       <c r="I323" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="J323" t="s">
         <v>841</v>
@@ -14953,10 +14956,10 @@
         <v>53901.0</v>
       </c>
       <c r="B324" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C324" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D324" t="s">
         <v>43</v>
@@ -14968,7 +14971,7 @@
         <v>139</v>
       </c>
       <c r="G324" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H324" t="s">
         <v>38</v>
@@ -14988,10 +14991,10 @@
         <v>64002.0</v>
       </c>
       <c r="B325" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C325" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D325" t="s">
         <v>70</v>
@@ -15003,16 +15006,16 @@
         <v>45</v>
       </c>
       <c r="G325" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H325" t="s">
         <v>38</v>
       </c>
       <c r="I325" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="J325" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="K325" t="s">
         <v>2</v>
@@ -15023,7 +15026,7 @@
         <v>62701.0</v>
       </c>
       <c r="B326" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C326" t="s">
         <v>843</v>
@@ -15044,7 +15047,7 @@
         <v>47</v>
       </c>
       <c r="I326" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="J326" t="s">
         <v>49</v>
@@ -15058,7 +15061,7 @@
         <v>63801.0</v>
       </c>
       <c r="B327" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C327" t="s">
         <v>292</v>
@@ -15073,7 +15076,7 @@
         <v>45</v>
       </c>
       <c r="G327" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H327" t="s">
         <v>38</v>
@@ -15093,10 +15096,10 @@
         <v>64401.0</v>
       </c>
       <c r="B328" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C328" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D328" t="s">
         <v>35</v>
@@ -15108,16 +15111,16 @@
         <v>45</v>
       </c>
       <c r="G328" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H328" t="s">
         <v>38</v>
       </c>
       <c r="I328" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="J328" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="K328" t="s">
         <v>2</v>
@@ -15128,31 +15131,31 @@
         <v>63901.0</v>
       </c>
       <c r="B329" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C329" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D329" t="s">
+        <v>43</v>
+      </c>
+      <c r="E329" t="s">
+        <v>43</v>
+      </c>
+      <c r="F329" t="s">
+        <v>45</v>
+      </c>
+      <c r="G329" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H329" t="s">
+        <v>38</v>
+      </c>
+      <c r="I329" t="s">
+        <v>1095</v>
+      </c>
+      <c r="J329" t="s">
         <v>1104</v>
-      </c>
-      <c r="C329" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D329" t="s">
-        <v>43</v>
-      </c>
-      <c r="E329" t="s">
-        <v>43</v>
-      </c>
-      <c r="F329" t="s">
-        <v>45</v>
-      </c>
-      <c r="G329" t="s">
-        <v>1106</v>
-      </c>
-      <c r="H329" t="s">
-        <v>38</v>
-      </c>
-      <c r="I329" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J329" t="s">
-        <v>1103</v>
       </c>
       <c r="K329" t="s">
         <v>2</v>
@@ -15163,10 +15166,10 @@
         <v>62901.0</v>
       </c>
       <c r="B330" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C330" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D330" t="s">
         <v>43</v>
@@ -15178,13 +15181,13 @@
         <v>45</v>
       </c>
       <c r="G330" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H330" t="s">
         <v>38</v>
       </c>
       <c r="I330" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="J330" t="s">
         <v>948</v>
@@ -15198,10 +15201,10 @@
         <v>61001.0</v>
       </c>
       <c r="B331" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C331" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D331" t="s">
         <v>44</v>
@@ -15233,10 +15236,10 @@
         <v>61901.0</v>
       </c>
       <c r="B332" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C332" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D332" t="s">
         <v>43</v>
@@ -15248,7 +15251,7 @@
         <v>45</v>
       </c>
       <c r="G332" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H332" t="s">
         <v>38</v>
@@ -15257,7 +15260,7 @@
         <v>254</v>
       </c>
       <c r="J332" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="K332" t="s">
         <v>2</v>
@@ -15268,10 +15271,10 @@
         <v>62301.0</v>
       </c>
       <c r="B333" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C333" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D333" t="s">
         <v>69</v>
@@ -15280,10 +15283,10 @@
         <v>69</v>
       </c>
       <c r="F333" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="G333" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H333" t="s">
         <v>38</v>
@@ -15292,7 +15295,7 @@
         <v>410</v>
       </c>
       <c r="J333" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="K333" t="s">
         <v>2</v>
@@ -15318,7 +15321,7 @@
         <v>45</v>
       </c>
       <c r="G334" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="H334" t="s">
         <v>47</v>
@@ -15338,7 +15341,7 @@
         <v>63401.0</v>
       </c>
       <c r="B335" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C335" t="s">
         <v>305</v>
@@ -15353,7 +15356,7 @@
         <v>45</v>
       </c>
       <c r="G335" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H335" t="s">
         <v>38</v>
@@ -15362,7 +15365,7 @@
         <v>410</v>
       </c>
       <c r="J335" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="K335" t="s">
         <v>2</v>
@@ -15373,10 +15376,10 @@
         <v>60501.0</v>
       </c>
       <c r="B336" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C336" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D336" t="s">
         <v>69</v>
@@ -15388,13 +15391,13 @@
         <v>45</v>
       </c>
       <c r="G336" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H336" t="s">
         <v>47</v>
       </c>
       <c r="I336" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="J336" t="s">
         <v>49</v>
@@ -15408,10 +15411,10 @@
         <v>64801.0</v>
       </c>
       <c r="B337" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C337" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D337" t="s">
         <v>43</v>
@@ -15429,10 +15432,10 @@
         <v>38</v>
       </c>
       <c r="I337" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="J337" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="K337" t="s">
         <v>2</v>
@@ -15443,31 +15446,31 @@
         <v>68501.0</v>
       </c>
       <c r="B338" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C338" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D338" t="s">
+        <v>43</v>
+      </c>
+      <c r="E338" t="s">
+        <v>43</v>
+      </c>
+      <c r="F338" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G338" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H338" t="s">
+        <v>38</v>
+      </c>
+      <c r="I338" t="s">
+        <v>1132</v>
+      </c>
+      <c r="J338" t="s">
         <v>1133</v>
-      </c>
-      <c r="C338" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D338" t="s">
-        <v>43</v>
-      </c>
-      <c r="E338" t="s">
-        <v>43</v>
-      </c>
-      <c r="F338" t="s">
-        <v>1135</v>
-      </c>
-      <c r="G338" t="s">
-        <v>1136</v>
-      </c>
-      <c r="H338" t="s">
-        <v>38</v>
-      </c>
-      <c r="I338" t="s">
-        <v>1131</v>
-      </c>
-      <c r="J338" t="s">
-        <v>1132</v>
       </c>
       <c r="K338" t="s">
         <v>2</v>
@@ -15478,31 +15481,31 @@
         <v>67301.0</v>
       </c>
       <c r="B339" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C339" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D339" t="s">
+        <v>43</v>
+      </c>
+      <c r="E339" t="s">
+        <v>43</v>
+      </c>
+      <c r="F339" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G339" t="s">
         <v>1137</v>
       </c>
-      <c r="C339" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D339" t="s">
-        <v>43</v>
-      </c>
-      <c r="E339" t="s">
-        <v>43</v>
-      </c>
-      <c r="F339" t="s">
-        <v>1135</v>
-      </c>
-      <c r="G339" t="s">
-        <v>1136</v>
-      </c>
       <c r="H339" t="s">
         <v>38</v>
       </c>
       <c r="I339" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="J339" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="K339" t="s">
         <v>2</v>
@@ -15513,10 +15516,10 @@
         <v>66301.0</v>
       </c>
       <c r="B340" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C340" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D340" t="s">
         <v>43</v>
@@ -15528,13 +15531,13 @@
         <v>45</v>
       </c>
       <c r="G340" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H340" t="s">
         <v>38</v>
       </c>
       <c r="I340" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="J340" t="s">
         <v>432</v>
@@ -15548,10 +15551,10 @@
         <v>67101.0</v>
       </c>
       <c r="B341" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="C341" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D341" t="s">
         <v>69</v>
@@ -15563,13 +15566,13 @@
         <v>45</v>
       </c>
       <c r="G341" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H341" t="s">
         <v>47</v>
       </c>
       <c r="I341" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="J341" t="s">
         <v>49</v>
@@ -15583,10 +15586,10 @@
         <v>62801.0</v>
       </c>
       <c r="B342" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C342" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D342" t="s">
         <v>69</v>
@@ -15598,16 +15601,16 @@
         <v>52</v>
       </c>
       <c r="G342" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="H342" t="s">
         <v>38</v>
       </c>
       <c r="I342" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="J342" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="K342" t="s">
         <v>2</v>
@@ -15618,10 +15621,10 @@
         <v>64901.0</v>
       </c>
       <c r="B343" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C343" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D343" t="s">
         <v>35</v>
@@ -15633,16 +15636,16 @@
         <v>45</v>
       </c>
       <c r="G343" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="H343" t="s">
         <v>38</v>
       </c>
       <c r="I343" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="J343" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="K343" t="s">
         <v>2</v>
@@ -15653,10 +15656,10 @@
         <v>63501.0</v>
       </c>
       <c r="B344" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C344" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D344" t="s">
         <v>35</v>
@@ -15668,16 +15671,16 @@
         <v>139</v>
       </c>
       <c r="G344" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H344" t="s">
         <v>38</v>
       </c>
       <c r="I344" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="J344" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="K344" t="s">
         <v>2</v>
@@ -15688,10 +15691,10 @@
         <v>63701.0</v>
       </c>
       <c r="B345" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C345" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D345" t="s">
         <v>69</v>
@@ -15703,16 +15706,16 @@
         <v>45</v>
       </c>
       <c r="G345" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H345" t="s">
         <v>38</v>
       </c>
       <c r="I345" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="J345" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="K345" t="s">
         <v>2</v>
@@ -15723,7 +15726,7 @@
         <v>68001.0</v>
       </c>
       <c r="B346" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C346" t="s">
         <v>272</v>
@@ -15738,16 +15741,16 @@
         <v>45</v>
       </c>
       <c r="G346" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="H346" t="s">
         <v>38</v>
       </c>
       <c r="I346" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="J346" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="K346" t="s">
         <v>2</v>
@@ -15758,10 +15761,10 @@
         <v>64301.0</v>
       </c>
       <c r="B347" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C347" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D347" t="s">
         <v>43</v>
@@ -15773,7 +15776,7 @@
         <v>45</v>
       </c>
       <c r="G347" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="H347" t="s">
         <v>38</v>
@@ -15782,7 +15785,7 @@
         <v>420</v>
       </c>
       <c r="J347" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="K347" t="s">
         <v>2</v>
@@ -15793,10 +15796,10 @@
         <v>63301.0</v>
       </c>
       <c r="B348" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C348" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D348" t="s">
         <v>69</v>
@@ -15814,10 +15817,10 @@
         <v>38</v>
       </c>
       <c r="I348" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="J348" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="K348" t="s">
         <v>2</v>
@@ -15828,10 +15831,10 @@
         <v>68201.0</v>
       </c>
       <c r="B349" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C349" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D349" t="s">
         <v>43</v>
@@ -15843,16 +15846,16 @@
         <v>139</v>
       </c>
       <c r="G349" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="H349" t="s">
         <v>38</v>
       </c>
       <c r="I349" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="J349" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="K349" t="s">
         <v>2</v>
@@ -15863,10 +15866,10 @@
         <v>58201.0</v>
       </c>
       <c r="B350" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="C350" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D350" t="s">
         <v>69</v>
@@ -15878,7 +15881,7 @@
         <v>45</v>
       </c>
       <c r="G350" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="H350" t="s">
         <v>38</v>
@@ -15887,7 +15890,7 @@
         <v>136</v>
       </c>
       <c r="J350" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="K350" t="s">
         <v>2</v>
@@ -15898,10 +15901,10 @@
         <v>56101.0</v>
       </c>
       <c r="B351" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C351" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D351" t="s">
         <v>35</v>
@@ -15913,7 +15916,7 @@
         <v>45</v>
       </c>
       <c r="G351" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H351" t="s">
         <v>38</v>
@@ -15922,7 +15925,7 @@
         <v>376</v>
       </c>
       <c r="J351" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="K351" t="s">
         <v>2</v>
@@ -15933,10 +15936,10 @@
         <v>57201.0</v>
       </c>
       <c r="B352" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C352" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D352" t="s">
         <v>70</v>
@@ -15948,7 +15951,7 @@
         <v>45</v>
       </c>
       <c r="G352" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="H352" t="s">
         <v>38</v>
@@ -15957,7 +15960,7 @@
         <v>376</v>
       </c>
       <c r="J352" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="K352" t="s">
         <v>2</v>
@@ -15968,7 +15971,7 @@
         <v>52801.0</v>
       </c>
       <c r="B353" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C353" t="s">
         <v>323</v>
@@ -15983,7 +15986,7 @@
         <v>45</v>
       </c>
       <c r="G353" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H353" t="s">
         <v>38</v>
@@ -15992,7 +15995,7 @@
         <v>136</v>
       </c>
       <c r="J353" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="K353" t="s">
         <v>2</v>
@@ -16003,10 +16006,10 @@
         <v>55401.0</v>
       </c>
       <c r="B354" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C354" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D354" t="s">
         <v>69</v>
@@ -16018,7 +16021,7 @@
         <v>45</v>
       </c>
       <c r="G354" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="H354" t="s">
         <v>38</v>
@@ -16027,7 +16030,7 @@
         <v>348</v>
       </c>
       <c r="J354" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="K354" t="s">
         <v>2</v>
@@ -16038,10 +16041,10 @@
         <v>58101.0</v>
       </c>
       <c r="B355" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="C355" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="D355" t="s">
         <v>69</v>
@@ -16053,7 +16056,7 @@
         <v>45</v>
       </c>
       <c r="G355" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H355" t="s">
         <v>38</v>
@@ -16062,7 +16065,7 @@
         <v>348</v>
       </c>
       <c r="J355" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="K355" t="s">
         <v>2</v>
@@ -16073,10 +16076,10 @@
         <v>54401.0</v>
       </c>
       <c r="B356" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C356" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D356" t="s">
         <v>43</v>
@@ -16088,7 +16091,7 @@
         <v>45</v>
       </c>
       <c r="G356" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="H356" t="s">
         <v>38</v>
@@ -16097,7 +16100,7 @@
         <v>106</v>
       </c>
       <c r="J356" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="K356" t="s">
         <v>2</v>
@@ -16108,10 +16111,10 @@
         <v>52601.0</v>
       </c>
       <c r="B357" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C357" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="D357" t="s">
         <v>35</v>
@@ -16123,7 +16126,7 @@
         <v>45</v>
       </c>
       <c r="G357" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H357" t="s">
         <v>38</v>
@@ -16132,7 +16135,7 @@
         <v>125</v>
       </c>
       <c r="J357" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="K357" t="s">
         <v>2</v>
@@ -16143,7 +16146,7 @@
         <v>56501.0</v>
       </c>
       <c r="B358" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C358" t="s">
         <v>191</v>
@@ -16158,16 +16161,16 @@
         <v>45</v>
       </c>
       <c r="G358" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H358" t="s">
         <v>38</v>
       </c>
       <c r="I358" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="J358" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="K358" t="s">
         <v>2</v>
@@ -16178,10 +16181,10 @@
         <v>55301.0</v>
       </c>
       <c r="B359" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C359" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D359" t="s">
         <v>35</v>
@@ -16202,7 +16205,7 @@
         <v>103</v>
       </c>
       <c r="J359" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="K359" t="s">
         <v>2</v>
@@ -16213,10 +16216,10 @@
         <v>55501.0</v>
       </c>
       <c r="B360" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="C360" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="D360" t="s">
         <v>43</v>
@@ -16228,7 +16231,7 @@
         <v>45</v>
       </c>
       <c r="G360" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H360" t="s">
         <v>38</v>
@@ -16237,7 +16240,7 @@
         <v>114</v>
       </c>
       <c r="J360" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="K360" t="s">
         <v>2</v>
@@ -16248,10 +16251,10 @@
         <v>61401.0</v>
       </c>
       <c r="B361" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C361" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="D361" t="s">
         <v>43</v>
@@ -16263,16 +16266,16 @@
         <v>45</v>
       </c>
       <c r="G361" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H361" t="s">
         <v>38</v>
       </c>
       <c r="I361" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="J361" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="K361" t="s">
         <v>2</v>
@@ -16283,7 +16286,7 @@
         <v>54801.0</v>
       </c>
       <c r="B362" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="C362" t="s">
         <v>877</v>
@@ -16298,13 +16301,13 @@
         <v>45</v>
       </c>
       <c r="G362" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H362" t="s">
         <v>47</v>
       </c>
       <c r="I362" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="J362" t="s">
         <v>49</v>
@@ -16318,10 +16321,10 @@
         <v>60301.0</v>
       </c>
       <c r="B363" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C363" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D363" t="s">
         <v>69</v>
@@ -16333,13 +16336,13 @@
         <v>45</v>
       </c>
       <c r="G363" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="H363" t="s">
         <v>47</v>
       </c>
       <c r="I363" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="J363" t="s">
         <v>49</v>
@@ -16353,10 +16356,10 @@
         <v>59401.0</v>
       </c>
       <c r="B364" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="C364" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="D364" t="s">
         <v>69</v>
@@ -16368,13 +16371,13 @@
         <v>45</v>
       </c>
       <c r="G364" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H364" t="s">
         <v>38</v>
       </c>
       <c r="I364" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="J364" t="s">
         <v>714</v>
@@ -16388,7 +16391,7 @@
         <v>54802.0</v>
       </c>
       <c r="B365" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="C365" t="s">
         <v>877</v>
@@ -16403,16 +16406,16 @@
         <v>45</v>
       </c>
       <c r="G365" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H365" t="s">
         <v>38</v>
       </c>
       <c r="I365" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="J365" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="K365" t="s">
         <v>2</v>
@@ -16423,10 +16426,10 @@
         <v>57101.0</v>
       </c>
       <c r="B366" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C366" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D366" t="s">
         <v>35</v>
@@ -16438,7 +16441,7 @@
         <v>45</v>
       </c>
       <c r="G366" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H366" t="s">
         <v>38</v>
@@ -16447,7 +16450,7 @@
         <v>393</v>
       </c>
       <c r="J366" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="K366" t="s">
         <v>2</v>
@@ -16458,10 +16461,10 @@
         <v>56901.0</v>
       </c>
       <c r="B367" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="C367" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D367" t="s">
         <v>69</v>
@@ -16473,16 +16476,16 @@
         <v>45</v>
       </c>
       <c r="G367" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="H367" t="s">
         <v>38</v>
       </c>
       <c r="I367" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="J367" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="K367" t="s">
         <v>2</v>
@@ -16493,10 +16496,10 @@
         <v>58901.0</v>
       </c>
       <c r="B368" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="C368" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="D368" t="s">
         <v>35</v>
@@ -16508,16 +16511,16 @@
         <v>45</v>
       </c>
       <c r="G368" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="H368" t="s">
         <v>38</v>
       </c>
       <c r="I368" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="J368" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="K368" t="s">
         <v>2</v>
@@ -16528,10 +16531,10 @@
         <v>56801.0</v>
       </c>
       <c r="B369" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C369" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D369" t="s">
         <v>35</v>
@@ -16543,16 +16546,16 @@
         <v>45</v>
       </c>
       <c r="G369" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="H369" t="s">
         <v>38</v>
       </c>
       <c r="I369" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="J369" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="K369" t="s">
         <v>2</v>
@@ -16563,10 +16566,10 @@
         <v>59601.0</v>
       </c>
       <c r="B370" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="C370" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="D370" t="s">
         <v>35</v>
@@ -16578,13 +16581,13 @@
         <v>45</v>
       </c>
       <c r="G370" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H370" t="s">
         <v>38</v>
       </c>
       <c r="I370" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="J370" t="s">
         <v>714</v>
@@ -16598,7 +16601,7 @@
         <v>59901.0</v>
       </c>
       <c r="B371" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C371" t="s">
         <v>68</v>
@@ -16613,16 +16616,16 @@
         <v>45</v>
       </c>
       <c r="G371" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H371" t="s">
         <v>38</v>
       </c>
       <c r="I371" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="J371" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="K371" t="s">
         <v>2</v>
@@ -16633,7 +16636,7 @@
         <v>57701.0</v>
       </c>
       <c r="B372" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C372" t="s">
         <v>880</v>
@@ -16648,16 +16651,16 @@
         <v>45</v>
       </c>
       <c r="G372" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H372" t="s">
         <v>38</v>
       </c>
       <c r="I372" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="J372" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="K372" t="s">
         <v>2</v>
@@ -16668,10 +16671,10 @@
         <v>59501.0</v>
       </c>
       <c r="B373" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="C373" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D373" t="s">
         <v>43</v>
@@ -16683,16 +16686,16 @@
         <v>45</v>
       </c>
       <c r="G373" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H373" t="s">
         <v>38</v>
       </c>
       <c r="I373" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="J373" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="K373" t="s">
         <v>2</v>
@@ -16703,10 +16706,10 @@
         <v>79701.0</v>
       </c>
       <c r="B374" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="C374" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="D374" t="s">
         <v>43</v>
@@ -16718,7 +16721,7 @@
         <v>139</v>
       </c>
       <c r="G374" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H374" t="s">
         <v>38</v>
@@ -16727,7 +16730,7 @@
         <v>553</v>
       </c>
       <c r="J374" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="K374" t="s">
         <v>2</v>
@@ -16738,10 +16741,10 @@
         <v>78101.0</v>
       </c>
       <c r="B375" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C375" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D375" t="s">
         <v>35</v>
@@ -16753,13 +16756,13 @@
         <v>45</v>
       </c>
       <c r="G375" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H375" t="s">
         <v>38</v>
       </c>
       <c r="I375" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="J375" t="s">
         <v>740</v>
@@ -16773,7 +16776,7 @@
         <v>78001.0</v>
       </c>
       <c r="B376" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C376" t="s">
         <v>571</v>
@@ -16788,7 +16791,7 @@
         <v>45</v>
       </c>
       <c r="G376" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H376" t="s">
         <v>38</v>
@@ -16808,7 +16811,7 @@
         <v>77701.0</v>
       </c>
       <c r="B377" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C377" t="s">
         <v>716</v>
@@ -16823,13 +16826,13 @@
         <v>45</v>
       </c>
       <c r="G377" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H377" t="s">
         <v>38</v>
       </c>
       <c r="I377" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="J377" t="s">
         <v>787</v>
@@ -16843,10 +16846,10 @@
         <v>78401.0</v>
       </c>
       <c r="B378" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C378" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D378" t="s">
         <v>533</v>
@@ -16858,13 +16861,13 @@
         <v>45</v>
       </c>
       <c r="G378" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H378" t="s">
         <v>38</v>
       </c>
       <c r="I378" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="J378" t="s">
         <v>513</v>
@@ -16878,10 +16881,10 @@
         <v>78901.0</v>
       </c>
       <c r="B379" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C379" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D379" t="s">
         <v>69</v>
@@ -16893,13 +16896,13 @@
         <v>45</v>
       </c>
       <c r="G379" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H379" t="s">
         <v>38</v>
       </c>
       <c r="I379" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="J379" t="s">
         <v>801</v>
@@ -16913,10 +16916,10 @@
         <v>73202.0</v>
       </c>
       <c r="B380" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C380" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="D380" t="s">
         <v>35</v>
@@ -16928,13 +16931,13 @@
         <v>45</v>
       </c>
       <c r="G380" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H380" t="s">
         <v>38</v>
       </c>
       <c r="I380" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="J380" t="s">
         <v>801</v>
@@ -16948,10 +16951,10 @@
         <v>76601.0</v>
       </c>
       <c r="B381" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="C381" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="D381" t="s">
         <v>43</v>
@@ -16963,16 +16966,16 @@
         <v>139</v>
       </c>
       <c r="G381" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H381" t="s">
         <v>38</v>
       </c>
       <c r="I381" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="J381" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="K381" t="s">
         <v>2</v>
@@ -16983,7 +16986,7 @@
         <v>75301.0</v>
       </c>
       <c r="B382" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C382" t="s">
         <v>790</v>
@@ -16998,13 +17001,13 @@
         <v>45</v>
       </c>
       <c r="G382" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H382" t="s">
         <v>47</v>
       </c>
       <c r="I382" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="J382" t="s">
         <v>49</v>
@@ -17018,7 +17021,7 @@
         <v>76901.0</v>
       </c>
       <c r="B383" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C383" t="s">
         <v>790</v>
@@ -17033,16 +17036,16 @@
         <v>45</v>
       </c>
       <c r="G383" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H383" t="s">
         <v>38</v>
       </c>
       <c r="I383" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="J383" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="K383" t="s">
         <v>2</v>
@@ -17053,10 +17056,10 @@
         <v>77101.0</v>
       </c>
       <c r="B384" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C384" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="D384" t="s">
         <v>44</v>
@@ -17068,13 +17071,13 @@
         <v>45</v>
       </c>
       <c r="G384" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H384" t="s">
         <v>38</v>
       </c>
       <c r="I384" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="J384" t="s">
         <v>964</v>
@@ -17088,7 +17091,7 @@
         <v>77201.0</v>
       </c>
       <c r="B385" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C385" t="s">
         <v>658</v>
@@ -17109,7 +17112,7 @@
         <v>38</v>
       </c>
       <c r="I385" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="J385" t="s">
         <v>792</v>
@@ -17123,10 +17126,10 @@
         <v>76501.0</v>
       </c>
       <c r="B386" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C386" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="D386" t="s">
         <v>43</v>
@@ -17138,16 +17141,16 @@
         <v>45</v>
       </c>
       <c r="G386" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H386" t="s">
         <v>38</v>
       </c>
       <c r="I386" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="J386" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="K386" t="s">
         <v>2</v>
@@ -17158,10 +17161,10 @@
         <v>79601.0</v>
       </c>
       <c r="B387" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="C387" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D387" t="s">
         <v>69</v>
@@ -17173,16 +17176,16 @@
         <v>45</v>
       </c>
       <c r="G387" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H387" t="s">
         <v>38</v>
       </c>
       <c r="I387" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="J387" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="K387" t="s">
         <v>2</v>
@@ -17193,7 +17196,7 @@
         <v>81501.0</v>
       </c>
       <c r="B388" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="C388" t="s">
         <v>765</v>
@@ -17214,10 +17217,10 @@
         <v>38</v>
       </c>
       <c r="I388" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="J388" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="K388" t="s">
         <v>2</v>
@@ -17228,10 +17231,10 @@
         <v>81001.0</v>
       </c>
       <c r="B389" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="C389" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="D389" t="s">
         <v>69</v>
@@ -17243,16 +17246,16 @@
         <v>52</v>
       </c>
       <c r="G389" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H389" t="s">
         <v>38</v>
       </c>
       <c r="I389" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="J389" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="K389" t="s">
         <v>2</v>
@@ -17284,10 +17287,10 @@
         <v>38</v>
       </c>
       <c r="I390" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="J390" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="K390" t="s">
         <v>2</v>
@@ -17298,10 +17301,10 @@
         <v>82001.0</v>
       </c>
       <c r="B391" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="C391" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D391" t="s">
         <v>43</v>
@@ -17313,7 +17316,7 @@
         <v>45</v>
       </c>
       <c r="G391" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H391" t="s">
         <v>38</v>
@@ -17322,7 +17325,7 @@
         <v>553</v>
       </c>
       <c r="J391" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="K391" t="s">
         <v>2</v>
@@ -17333,10 +17336,10 @@
         <v>78301.0</v>
       </c>
       <c r="B392" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="C392" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="D392" t="s">
         <v>69</v>
@@ -17348,7 +17351,7 @@
         <v>45</v>
       </c>
       <c r="G392" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H392" t="s">
         <v>38</v>
@@ -17357,7 +17360,7 @@
         <v>575</v>
       </c>
       <c r="J392" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="K392" t="s">
         <v>2</v>
@@ -17383,16 +17386,16 @@
         <v>52</v>
       </c>
       <c r="G393" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H393" t="s">
         <v>38</v>
       </c>
       <c r="I393" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="J393" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="K393" t="s">
         <v>2</v>
@@ -17403,10 +17406,10 @@
         <v>79101.0</v>
       </c>
       <c r="B394" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="C394" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D394" t="s">
         <v>70</v>
@@ -17418,16 +17421,16 @@
         <v>45</v>
       </c>
       <c r="G394" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H394" t="s">
         <v>38</v>
       </c>
       <c r="I394" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="J394" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="K394" t="s">
         <v>2</v>
@@ -17438,10 +17441,10 @@
         <v>81101.0</v>
       </c>
       <c r="B395" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C395" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D395" t="s">
         <v>70</v>
@@ -17453,16 +17456,16 @@
         <v>45</v>
       </c>
       <c r="G395" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H395" t="s">
         <v>38</v>
       </c>
       <c r="I395" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="J395" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="K395" t="s">
         <v>2</v>
@@ -17473,10 +17476,10 @@
         <v>80901.0</v>
       </c>
       <c r="B396" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C396" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D396" t="s">
         <v>43</v>
@@ -17488,13 +17491,13 @@
         <v>45</v>
       </c>
       <c r="G396" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H396" t="s">
         <v>38</v>
       </c>
       <c r="I396" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="J396" t="s">
         <v>772</v>
@@ -17508,7 +17511,7 @@
         <v>80201.0</v>
       </c>
       <c r="B397" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C397" t="s">
         <v>264</v>
@@ -17529,10 +17532,10 @@
         <v>38</v>
       </c>
       <c r="I397" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="J397" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="K397" t="s">
         <v>2</v>
@@ -17543,10 +17546,10 @@
         <v>80801.0</v>
       </c>
       <c r="B398" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C398" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D398" t="s">
         <v>43</v>
@@ -17558,13 +17561,13 @@
         <v>45</v>
       </c>
       <c r="G398" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H398" t="s">
         <v>38</v>
       </c>
       <c r="I398" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="J398" t="s">
         <v>586</v>
@@ -17578,10 +17581,10 @@
         <v>69801.0</v>
       </c>
       <c r="B399" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C399" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D399" t="s">
         <v>44</v>
@@ -17599,10 +17602,10 @@
         <v>38</v>
       </c>
       <c r="I399" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="J399" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="K399" t="s">
         <v>2</v>
@@ -17613,10 +17616,10 @@
         <v>70601.0</v>
       </c>
       <c r="B400" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C400" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="D400" t="s">
         <v>43</v>
@@ -17648,10 +17651,10 @@
         <v>67001.0</v>
       </c>
       <c r="B401" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C401" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="D401" t="s">
         <v>35</v>
@@ -17663,16 +17666,16 @@
         <v>45</v>
       </c>
       <c r="G401" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H401" t="s">
         <v>38</v>
       </c>
       <c r="I401" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="J401" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="K401" t="s">
         <v>2</v>
@@ -17683,10 +17686,10 @@
         <v>70301.0</v>
       </c>
       <c r="B402" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="C402" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="D402" t="s">
         <v>43</v>
@@ -17698,13 +17701,13 @@
         <v>45</v>
       </c>
       <c r="G402" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H402" t="s">
         <v>38</v>
       </c>
       <c r="I402" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="J402" t="s">
         <v>500</v>
@@ -17718,10 +17721,10 @@
         <v>71701.0</v>
       </c>
       <c r="B403" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="C403" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="D403" t="s">
         <v>35</v>
@@ -17753,10 +17756,10 @@
         <v>70901.0</v>
       </c>
       <c r="B404" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="C404" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D404" t="s">
         <v>69</v>
@@ -17768,7 +17771,7 @@
         <v>45</v>
       </c>
       <c r="G404" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H404" t="s">
         <v>47</v>
@@ -17788,7 +17791,7 @@
         <v>71601.0</v>
       </c>
       <c r="B405" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="C405" t="s">
         <v>100</v>
@@ -17803,7 +17806,7 @@
         <v>45</v>
       </c>
       <c r="G405" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H405" t="s">
         <v>38</v>
@@ -17823,10 +17826,10 @@
         <v>70101.0</v>
       </c>
       <c r="B406" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="C406" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="D406" t="s">
         <v>69</v>
@@ -17838,13 +17841,13 @@
         <v>45</v>
       </c>
       <c r="G406" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H406" t="s">
         <v>38</v>
       </c>
       <c r="I406" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="J406" t="s">
         <v>500</v>
@@ -17855,7 +17858,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B407" t="s">
         <v>304</v>
@@ -17873,16 +17876,16 @@
         <v>45</v>
       </c>
       <c r="G407" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H407" t="s">
         <v>38</v>
       </c>
       <c r="I407" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="J407" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="K407" t="s">
         <v>2</v>
@@ -17893,10 +17896,10 @@
         <v>69701.0</v>
       </c>
       <c r="B408" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="C408" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="D408" t="s">
         <v>35</v>
@@ -17908,13 +17911,13 @@
         <v>52</v>
       </c>
       <c r="G408" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H408" t="s">
         <v>47</v>
       </c>
       <c r="I408" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="J408" t="s">
         <v>49</v>
@@ -17928,10 +17931,10 @@
         <v>67501.0</v>
       </c>
       <c r="B409" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="C409" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="D409" t="s">
         <v>35</v>
@@ -17943,13 +17946,13 @@
         <v>45</v>
       </c>
       <c r="G409" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H409" t="s">
         <v>38</v>
       </c>
       <c r="I409" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="J409" t="s">
         <v>500</v>
@@ -17963,10 +17966,10 @@
         <v>69301.0</v>
       </c>
       <c r="B410" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="C410" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="D410" t="s">
         <v>35</v>
@@ -17978,13 +17981,13 @@
         <v>52</v>
       </c>
       <c r="G410" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H410" t="s">
         <v>38</v>
       </c>
       <c r="I410" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="J410" t="s">
         <v>500</v>
@@ -17998,10 +18001,10 @@
         <v>60001.0</v>
       </c>
       <c r="B411" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="C411" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D411" t="s">
         <v>43</v>
@@ -18010,16 +18013,16 @@
         <v>43</v>
       </c>
       <c r="F411" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="G411" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H411" t="s">
         <v>47</v>
       </c>
       <c r="I411" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="J411" t="s">
         <v>49</v>
@@ -18033,7 +18036,7 @@
         <v>74301.0</v>
       </c>
       <c r="B412" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="C412" t="s">
         <v>310</v>
@@ -18048,16 +18051,16 @@
         <v>45</v>
       </c>
       <c r="G412" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H412" t="s">
         <v>38</v>
       </c>
       <c r="I412" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="J412" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="K412" t="s">
         <v>2</v>
@@ -18068,7 +18071,7 @@
         <v>74701.0</v>
       </c>
       <c r="B413" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="C413" t="s">
         <v>804</v>
@@ -18083,16 +18086,16 @@
         <v>45</v>
       </c>
       <c r="G413" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H413" t="s">
         <v>38</v>
       </c>
       <c r="I413" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="J413" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="K413" t="s">
         <v>2</v>
@@ -18103,10 +18106,10 @@
         <v>72701.0</v>
       </c>
       <c r="B414" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="C414" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="D414" t="s">
         <v>43</v>
@@ -18118,13 +18121,13 @@
         <v>139</v>
       </c>
       <c r="G414" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H414" t="s">
         <v>47</v>
       </c>
       <c r="I414" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="J414" t="s">
         <v>49</v>
@@ -18138,7 +18141,7 @@
         <v>75901.0</v>
       </c>
       <c r="B415" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="C415" t="s">
         <v>330</v>
@@ -18153,13 +18156,13 @@
         <v>45</v>
       </c>
       <c r="G415" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H415" t="s">
         <v>38</v>
       </c>
       <c r="I415" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="J415" t="s">
         <v>740</v>
@@ -18173,10 +18176,10 @@
         <v>73901.0</v>
       </c>
       <c r="B416" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="C416" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="D416" t="s">
         <v>35</v>
@@ -18194,7 +18197,7 @@
         <v>38</v>
       </c>
       <c r="I416" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="J416" t="s">
         <v>883</v>
@@ -18208,7 +18211,7 @@
         <v>71901.0</v>
       </c>
       <c r="B417" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C417" t="s">
         <v>813</v>
@@ -18223,16 +18226,16 @@
         <v>45</v>
       </c>
       <c r="G417" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H417" t="s">
         <v>38</v>
       </c>
       <c r="I417" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="J417" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="K417" t="s">
         <v>2</v>
@@ -18243,10 +18246,10 @@
         <v>73201.0</v>
       </c>
       <c r="B418" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C418" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="D418" t="s">
         <v>35</v>
@@ -18264,7 +18267,7 @@
         <v>38</v>
       </c>
       <c r="I418" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="J418" t="s">
         <v>718</v>
@@ -18278,10 +18281,10 @@
         <v>72501.0</v>
       </c>
       <c r="B419" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="C419" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D419" t="s">
         <v>69</v>
@@ -18293,16 +18296,16 @@
         <v>52</v>
       </c>
       <c r="G419" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H419" t="s">
         <v>38</v>
       </c>
       <c r="I419" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="J419" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="K419" t="s">
         <v>2</v>
@@ -18313,10 +18316,10 @@
         <v>74201.0</v>
       </c>
       <c r="B420" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="C420" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="D420" t="s">
         <v>43</v>
@@ -18328,13 +18331,13 @@
         <v>45</v>
       </c>
       <c r="G420" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H420" t="s">
         <v>38</v>
       </c>
       <c r="I420" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="J420" t="s">
         <v>693</v>
@@ -18348,10 +18351,10 @@
         <v>71801.0</v>
       </c>
       <c r="B421" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="C421" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="D421" t="s">
         <v>43</v>
@@ -18363,13 +18366,13 @@
         <v>45</v>
       </c>
       <c r="G421" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H421" t="s">
         <v>38</v>
       </c>
       <c r="I421" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="J421" t="s">
         <v>710</v>
@@ -18383,10 +18386,10 @@
         <v>73301.0</v>
       </c>
       <c r="B422" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="C422" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="D422" t="s">
         <v>43</v>
@@ -18398,13 +18401,13 @@
         <v>139</v>
       </c>
       <c r="G422" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H422" t="s">
         <v>47</v>
       </c>
       <c r="I422" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="J422" t="s">
         <v>49</v>
@@ -18418,10 +18421,10 @@
         <v>73501.0</v>
       </c>
       <c r="B423" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="C423" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="D423" t="s">
         <v>43</v>
@@ -18433,13 +18436,13 @@
         <v>45</v>
       </c>
       <c r="G423" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H423" t="s">
         <v>38</v>
       </c>
       <c r="I423" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="J423" t="s">
         <v>710</v>
@@ -18450,18 +18453,18 @@
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/contratos/latest.xlsx
+++ b/xlsx/contratos/latest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4066" uniqueCount="1412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4076" uniqueCount="1415">
   <si>
     <t>Contrato</t>
   </si>
@@ -387,7 +387,7 @@
     <t>Douglas José de Paula</t>
   </si>
   <si>
-    <t>EFRAIN RIBEIRO</t>
+    <t>Efraim Ribeiro da Silva</t>
   </si>
   <si>
     <t>R$ 39123.85</t>
@@ -2853,6 +2853,15 @@
     <t>11/08/2026</t>
   </si>
   <si>
+    <t>1017 - MO LUIS FERNANDO DA SILVA NEVE - 22/09/26</t>
+  </si>
+  <si>
+    <t>MO LUIS FERNANDO DA SILVA NEVES</t>
+  </si>
+  <si>
+    <t>08/12/2026</t>
+  </si>
+  <si>
     <t>1025 - Julio Cezar Pereira - 28/09/26</t>
   </si>
   <si>
@@ -2865,88 +2874,328 @@
     <t>R$ 41000.00</t>
   </si>
   <si>
+    <t>1023 - Thiago Degola - 25/09/26</t>
+  </si>
+  <si>
+    <t>Thiago Souza Dias Degola</t>
+  </si>
+  <si>
+    <t>30/11/2026</t>
+  </si>
+  <si>
+    <t>1009 - Mariana Andrade Derossi - 17/09/26</t>
+  </si>
+  <si>
+    <t>Mariana Andrade Derossi</t>
+  </si>
+  <si>
+    <t>R$ 67698.84</t>
+  </si>
+  <si>
+    <t>18/02/2027</t>
+  </si>
+  <si>
+    <t>1029 - CARLA EMÍLIA DE OLIVEIRA SOUZA FERREIRA - 01/10/26</t>
+  </si>
+  <si>
+    <t>CARLA EMÍLIA DE OLIVEIRA SOUZA FERREIRA</t>
+  </si>
+  <si>
+    <t>R$ 178.08</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t>15/12/2026</t>
+  </si>
+  <si>
+    <t>1021 - RICARDO LUIZ VALIM GOMES - 1831401081 - 24/09/26</t>
+  </si>
+  <si>
+    <t>RICARDO LUIZ VALIM GOMES</t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
+  </si>
+  <si>
+    <t>1003 - Tatiana - 14/09/26</t>
+  </si>
+  <si>
+    <t>Tatiana Wagner Kissmann</t>
+  </si>
+  <si>
+    <t>R$ 29900.00</t>
+  </si>
+  <si>
+    <t>26/11/2026</t>
+  </si>
+  <si>
     <t>1011 - Noel Pt ( indicação Paulo Portugues) - 21/09/26</t>
   </si>
   <si>
     <t>NOEL DA COSTA LEITAO</t>
   </si>
   <si>
-    <t>1017 - MO LUIS FERNANDO DA SILVA NEVE - 22/09/26</t>
-  </si>
-  <si>
-    <t>MO LUIS FERNANDO DA SILVA NEVES</t>
-  </si>
-  <si>
-    <t>08/12/2026</t>
-  </si>
-  <si>
-    <t>1023 - Thiago Degola - 25/09/26</t>
-  </si>
-  <si>
-    <t>Thiago Souza Dias Degola</t>
-  </si>
-  <si>
-    <t>30/11/2026</t>
-  </si>
-  <si>
-    <t>1009 - Mariana Andrade Derossi - 17/09/26</t>
-  </si>
-  <si>
-    <t>Mariana Andrade Derossi</t>
-  </si>
-  <si>
-    <t>R$ 67698.84</t>
-  </si>
-  <si>
-    <t>18/02/2027</t>
-  </si>
-  <si>
-    <t>1003 - Tatiana - 14/09/26</t>
-  </si>
-  <si>
-    <t>Tatiana Wagner Kissmann</t>
-  </si>
-  <si>
-    <t>R$ 29900.00</t>
-  </si>
-  <si>
-    <t>25/09/2026</t>
-  </si>
-  <si>
-    <t>26/11/2026</t>
+    <t>1018 - FRED BATISTA RIBEIRO - 24/09/26</t>
+  </si>
+  <si>
+    <t>FRED BATISTA RIBEIRO</t>
+  </si>
+  <si>
+    <t>R$ 24432.00</t>
+  </si>
+  <si>
+    <t>26/09/2026</t>
+  </si>
+  <si>
+    <t>1012 - Moema Stefany e Guilherme Nune - 21/09/26</t>
+  </si>
+  <si>
+    <t>Guilherme Nunes araujo</t>
+  </si>
+  <si>
+    <t>R$ 15000.00</t>
+  </si>
+  <si>
+    <t>28/02/2027</t>
   </si>
   <si>
     <t>979 - Vera lucia Prado Mattos - 31/08/26</t>
   </si>
   <si>
-    <t>1012 - Moema Stefany e Guilherme Nune - 21/09/26</t>
-  </si>
-  <si>
-    <t>Guilherme Nunes araujo</t>
-  </si>
-  <si>
-    <t>R$ 15000.00</t>
-  </si>
-  <si>
-    <t>26/09/2026</t>
-  </si>
-  <si>
-    <t>28/02/2027</t>
-  </si>
-  <si>
-    <t>1021 - RICARDO LUIZ VALIM GOMES - 1831401081 - 24/09/26</t>
-  </si>
-  <si>
-    <t>RICARDO LUIZ VALIM GOMES</t>
-  </si>
-  <si>
-    <t>1018 - FRED BATISTA RIBEIRO - 24/09/26</t>
-  </si>
-  <si>
-    <t>FRED BATISTA RIBEIRO</t>
-  </si>
-  <si>
-    <t>R$ 24432.00</t>
+    <t>1057 - DANIELA IDA MENEGATTI MILANO - 23/10/26</t>
+  </si>
+  <si>
+    <t>R$ 13843.12</t>
+  </si>
+  <si>
+    <t>24/10/2026</t>
+  </si>
+  <si>
+    <t>1044 - MO REGINA RURIKO - 14/10/26</t>
+  </si>
+  <si>
+    <t>REGINA RURIKO TATEIGI</t>
+  </si>
+  <si>
+    <t>R$ 29700.00</t>
+  </si>
+  <si>
+    <t>19/10/2026</t>
+  </si>
+  <si>
+    <t>1051 - Claudio Wasserman - 17/10/26</t>
+  </si>
+  <si>
+    <t>Claudio Wasserman</t>
+  </si>
+  <si>
+    <t>R$ 50900.00</t>
+  </si>
+  <si>
+    <t>17/12/2026</t>
+  </si>
+  <si>
+    <t>1055 - Willian Rodrigues Lima - 21/10/26</t>
+  </si>
+  <si>
+    <t>Willian Rodrigues Lima</t>
+  </si>
+  <si>
+    <t>27/02/2027</t>
+  </si>
+  <si>
+    <t>1060 - Claudio Wasserman - 26/10/26</t>
+  </si>
+  <si>
+    <t>R$ 19333.59</t>
+  </si>
+  <si>
+    <t>05/01/2027</t>
+  </si>
+  <si>
+    <t>1035 - IL HEE PARK - 07/10/26</t>
+  </si>
+  <si>
+    <t>R$ 3500.00</t>
+  </si>
+  <si>
+    <t>1047 - Patrícia Santos da Silva - 15/10/26</t>
+  </si>
+  <si>
+    <t>R$ 1053.00</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>23/12/2026</t>
+  </si>
+  <si>
+    <t>1038 - ADRIANA REGO BARROS MAGALHÃES - 13/10/26</t>
+  </si>
+  <si>
+    <t>ADRIANA REGO BARROS MAGALHÃES</t>
+  </si>
+  <si>
+    <t>R$ 1700.00</t>
+  </si>
+  <si>
+    <t>1053 - Complemento - Elaine Massumi Higashi</t>
+  </si>
+  <si>
+    <t>R$ 5180.00</t>
+  </si>
+  <si>
+    <t>1050 - Portas em vidro</t>
+  </si>
+  <si>
+    <t>R$ 1931.16</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>1048 - Venda Avulsa - VIVIAN MOURA BENIFICA GAZOLA</t>
+  </si>
+  <si>
+    <t>VIVIAN MOURA BENIFICA GAZOLA</t>
+  </si>
+  <si>
+    <t>R$ 340.52</t>
+  </si>
+  <si>
+    <t>943 - EDUARDO CASULO ALVAREZ - 12/08/26</t>
+  </si>
+  <si>
+    <t>12/08/2026</t>
+  </si>
+  <si>
+    <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>973 - Rodrigo Lucas Scaff - 27/08/26</t>
+  </si>
+  <si>
+    <t>R$ 915.00</t>
+  </si>
+  <si>
+    <t>04/11/2026</t>
+  </si>
+  <si>
+    <t>968 - Venda Avulsa - FL818 EMPREENDIMENTOS E PARTICIPAÇÕES</t>
+  </si>
+  <si>
+    <t>R$ 281.69</t>
+  </si>
+  <si>
+    <t>25/08/2026</t>
+  </si>
+  <si>
+    <t>02/11/2026</t>
+  </si>
+  <si>
+    <t>964 - Venda Avulsa - ALESSANDRA MONTEMURRO CORREA</t>
+  </si>
+  <si>
+    <t>R$ 4647.95</t>
+  </si>
+  <si>
+    <t>24/08/2026</t>
+  </si>
+  <si>
+    <t>31/08/2026</t>
+  </si>
+  <si>
+    <t>961 - ADRIANA BARROS - 24/08/26</t>
+  </si>
+  <si>
+    <t>R$ 24990.00</t>
+  </si>
+  <si>
+    <t>949 - Graziela Trindade - 15/08/26</t>
+  </si>
+  <si>
+    <t>Graziela Lima da Trindade</t>
+  </si>
+  <si>
+    <t>R$ 9068.26</t>
+  </si>
+  <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t>20/02/2027</t>
+  </si>
+  <si>
+    <t>965 - Lucas Machado - 24/08/26</t>
+  </si>
+  <si>
+    <t>Lucas Prado Galvão Machado</t>
+  </si>
+  <si>
+    <t>R$ 29027.98</t>
+  </si>
+  <si>
+    <t>29/08/2026</t>
+  </si>
+  <si>
+    <t>30/06/2027</t>
+  </si>
+  <si>
+    <t>934 - COMPLEMENTO DE PROJETO EXECUTIVO</t>
+  </si>
+  <si>
+    <t>R$ 2364.64</t>
+  </si>
+  <si>
+    <t>923 - Waleska Simoes Corrêa - 04/08/26</t>
+  </si>
+  <si>
+    <t>Waleska Simoes Coorea</t>
+  </si>
+  <si>
+    <t>953 - Paulo José dos santos Lacerda - 19/08/26</t>
+  </si>
+  <si>
+    <t>Paulo José dos santos Lacerda</t>
+  </si>
+  <si>
+    <t>R$ 600.00</t>
+  </si>
+  <si>
+    <t>21/08/2026</t>
+  </si>
+  <si>
+    <t>29/10/2026</t>
+  </si>
+  <si>
+    <t>950 - Alessandra Lazzarini - 17/08/26</t>
+  </si>
+  <si>
+    <t>Eliana Rigotto Lazzarini</t>
+  </si>
+  <si>
+    <t>19/08/2026</t>
+  </si>
+  <si>
+    <t>919 - Kathleen dos Santos Andrade - 03/08/26</t>
+  </si>
+  <si>
+    <t>Lierton Bezerra gomes</t>
+  </si>
+  <si>
+    <t>R$ 41915.18</t>
+  </si>
+  <si>
+    <t>944 - Moema Wilza Silva Zake - 13/08/26</t>
+  </si>
+  <si>
+    <t>Wilza Silva Zake</t>
+  </si>
+  <si>
+    <t>14/08/2026</t>
   </si>
   <si>
     <t>1005 - RAFAEL SUNDFELD DE ALENCAR - 15/09/26</t>
@@ -2961,259 +3210,67 @@
     <t>22/09/2026</t>
   </si>
   <si>
-    <t>1044 - MO REGINA RURIKO - 14/10/26</t>
-  </si>
-  <si>
-    <t>REGINA RURIKO TATEIGI</t>
-  </si>
-  <si>
-    <t>R$ 29700.00</t>
-  </si>
-  <si>
-    <t>19/10/2026</t>
-  </si>
-  <si>
-    <t>1051 - Claudio Wasserman - 17/10/26</t>
-  </si>
-  <si>
-    <t>Claudio Wasserman</t>
-  </si>
-  <si>
-    <t>R$ 50900.00</t>
-  </si>
-  <si>
-    <t>17/12/2026</t>
-  </si>
-  <si>
-    <t>1053 - Complemento - Elaine Massumi Higashi</t>
-  </si>
-  <si>
-    <t>R$ 5180.00</t>
-  </si>
-  <si>
-    <t>1057 - DANIELA IDA MENEGATTI MILANO - 23/10/26</t>
-  </si>
-  <si>
-    <t>R$ 13843.12</t>
-  </si>
-  <si>
-    <t>24/10/2026</t>
-  </si>
-  <si>
-    <t>01/01/2027</t>
-  </si>
-  <si>
-    <t>1055 - Willian Rodrigues Lima - 21/10/26</t>
-  </si>
-  <si>
-    <t>Willian Rodrigues Lima</t>
-  </si>
-  <si>
-    <t>1029 - CARLA EMÍLIA DE OLIVEIRA SOUZA FERREIRA - 01/10/26</t>
-  </si>
-  <si>
-    <t>CARLA EMÍLIA DE OLIVEIRA SOUZA FERREIRA</t>
-  </si>
-  <si>
-    <t>R$ 178.08</t>
-  </si>
-  <si>
-    <t>07/10/2026</t>
-  </si>
-  <si>
-    <t>15/12/2026</t>
-  </si>
-  <si>
-    <t>1038 - ADRIANA REGO BARROS MAGALHÃES - 13/10/26</t>
-  </si>
-  <si>
-    <t>ADRIANA REGO BARROS MAGALHÃES</t>
-  </si>
-  <si>
-    <t>R$ 1700.00</t>
-  </si>
-  <si>
-    <t>15/10/2026</t>
-  </si>
-  <si>
-    <t>23/12/2026</t>
-  </si>
-  <si>
-    <t>1035 - IL HEE PARK - 07/10/26</t>
-  </si>
-  <si>
-    <t>R$ 3500.00</t>
-  </si>
-  <si>
-    <t>1050 - Portas em vidro</t>
-  </si>
-  <si>
-    <t>R$ 1931.16</t>
-  </si>
-  <si>
-    <t>16/10/2026</t>
-  </si>
-  <si>
-    <t>1047 - Patrícia Santos da Silva - 15/10/26</t>
-  </si>
-  <si>
-    <t>R$ 1053.00</t>
-  </si>
-  <si>
-    <t>1048 - Venda Avulsa - VIVIAN MOURA BENIFICA GAZOLA</t>
-  </si>
-  <si>
-    <t>VIVIAN MOURA BENIFICA GAZOLA</t>
-  </si>
-  <si>
-    <t>R$ 340.52</t>
-  </si>
-  <si>
-    <t>943 - EDUARDO CASULO ALVAREZ - 12/08/26</t>
-  </si>
-  <si>
-    <t>12/08/2026</t>
-  </si>
-  <si>
-    <t>20/10/2026</t>
-  </si>
-  <si>
-    <t>968 - Venda Avulsa - FL818 EMPREENDIMENTOS E PARTICIPAÇÕES</t>
-  </si>
-  <si>
-    <t>R$ 281.69</t>
-  </si>
-  <si>
-    <t>25/08/2026</t>
-  </si>
-  <si>
-    <t>02/11/2026</t>
-  </si>
-  <si>
-    <t>964 - Venda Avulsa - ALESSANDRA MONTEMURRO CORREA</t>
-  </si>
-  <si>
-    <t>R$ 4647.95</t>
-  </si>
-  <si>
-    <t>24/08/2026</t>
-  </si>
-  <si>
-    <t>31/08/2026</t>
-  </si>
-  <si>
-    <t>953 - Paulo José dos santos Lacerda - 19/08/26</t>
-  </si>
-  <si>
-    <t>Paulo José dos santos Lacerda</t>
-  </si>
-  <si>
-    <t>R$ 600.00</t>
-  </si>
-  <si>
-    <t>21/08/2026</t>
-  </si>
-  <si>
-    <t>29/10/2026</t>
-  </si>
-  <si>
-    <t>973 - Rodrigo Lucas Scaff - 27/08/26</t>
-  </si>
-  <si>
-    <t>R$ 915.00</t>
-  </si>
-  <si>
-    <t>04/11/2026</t>
-  </si>
-  <si>
-    <t>961 - ADRIANA BARROS - 24/08/26</t>
-  </si>
-  <si>
-    <t>R$ 24990.00</t>
-  </si>
-  <si>
-    <t>949 - Graziela Trindade - 15/08/26</t>
-  </si>
-  <si>
-    <t>Graziela Lima da Trindade</t>
-  </si>
-  <si>
-    <t>R$ 9068.26</t>
-  </si>
-  <si>
-    <t>28/08/2026</t>
-  </si>
-  <si>
-    <t>20/02/2027</t>
-  </si>
-  <si>
-    <t>934 - COMPLEMENTO DE PROJETO EXECUTIVO</t>
-  </si>
-  <si>
-    <t>R$ 2364.64</t>
-  </si>
-  <si>
-    <t>923 - Waleska Simoes Corrêa - 04/08/26</t>
-  </si>
-  <si>
-    <t>Waleska Simoes Coorea</t>
-  </si>
-  <si>
-    <t>950 - Alessandra Lazzarini - 17/08/26</t>
-  </si>
-  <si>
-    <t>Eliana Rigotto Lazzarini</t>
-  </si>
-  <si>
-    <t>19/08/2026</t>
-  </si>
-  <si>
-    <t>919 - Kathleen dos Santos Andrade - 03/08/26</t>
-  </si>
-  <si>
-    <t>Lierton Bezerra gomes</t>
-  </si>
-  <si>
-    <t>R$ 41915.18</t>
-  </si>
-  <si>
-    <t>944 - Moema Wilza Silva Zake - 13/08/26</t>
-  </si>
-  <si>
-    <t>Wilza Silva Zake</t>
-  </si>
-  <si>
-    <t>14/08/2026</t>
+    <t>969 - DANIELA IDA MENEGATTI MILANO - 26/08/26</t>
+  </si>
+  <si>
+    <t>R$ 16000.00</t>
+  </si>
+  <si>
+    <t>12/09/2026</t>
+  </si>
+  <si>
+    <t>954 - LUCIANA DAMASIO - 20/08/26</t>
+  </si>
+  <si>
+    <t>FABIO FERREIRA DAMASIO</t>
+  </si>
+  <si>
+    <t>R$ 46800.00</t>
+  </si>
+  <si>
+    <t>09/09/2026</t>
+  </si>
+  <si>
+    <t>966 - Enno Winter - 25/08/26</t>
+  </si>
+  <si>
+    <t>Enno Albert Winter</t>
+  </si>
+  <si>
+    <t>R$ 41216.84</t>
+  </si>
+  <si>
+    <t>30/12/2026</t>
   </si>
   <si>
     <t>1014 - Enno Albert Winter sala 1212 - 21/09/26</t>
   </si>
   <si>
-    <t>Enno Albert Winter</t>
-  </si>
-  <si>
     <t>R$ 32583.16</t>
   </si>
   <si>
-    <t>969 - DANIELA IDA MENEGATTI MILANO - 26/08/26</t>
-  </si>
-  <si>
-    <t>R$ 16000.00</t>
-  </si>
-  <si>
-    <t>12/09/2026</t>
-  </si>
-  <si>
-    <t>954 - LUCIANA DAMASIO - 20/08/26</t>
-  </si>
-  <si>
-    <t>FABIO FERREIRA DAMASIO</t>
-  </si>
-  <si>
-    <t>R$ 46800.00</t>
-  </si>
-  <si>
-    <t>09/09/2026</t>
+    <t>974 - Alexandre Gleyson - 28/08/26</t>
+  </si>
+  <si>
+    <t>Alexandre Gleyson Araujo da Silva</t>
+  </si>
+  <si>
+    <t>R$ 63824.33</t>
+  </si>
+  <si>
+    <t>10/12/2026</t>
+  </si>
+  <si>
+    <t>08/11/2026</t>
+  </si>
+  <si>
+    <t>976 - MO FELIPE SCHIAVON - 28/08/26</t>
+  </si>
+  <si>
+    <t>FELIPE VANDERLINDE SCHIAVON</t>
+  </si>
+  <si>
+    <t>R$ 8543.00</t>
   </si>
   <si>
     <t>957 - Alexandre Augusto Silva Machado - 21/08/26</t>
@@ -3225,51 +3282,6 @@
     <t>19/01/2027</t>
   </si>
   <si>
-    <t>966 - Enno Winter - 25/08/26</t>
-  </si>
-  <si>
-    <t>R$ 41216.84</t>
-  </si>
-  <si>
-    <t>30/12/2026</t>
-  </si>
-  <si>
-    <t>965 - Lucas Machado - 24/08/26</t>
-  </si>
-  <si>
-    <t>Lucas Prado Galvão Machado</t>
-  </si>
-  <si>
-    <t>R$ 29027.98</t>
-  </si>
-  <si>
-    <t>29/08/2026</t>
-  </si>
-  <si>
-    <t>30/06/2027</t>
-  </si>
-  <si>
-    <t>976 - MO FELIPE SCHIAVON - 28/08/26</t>
-  </si>
-  <si>
-    <t>FELIPE VANDERLINDE SCHIAVON</t>
-  </si>
-  <si>
-    <t>R$ 8543.00</t>
-  </si>
-  <si>
-    <t>974 - Alexandre Gleyson - 28/08/26</t>
-  </si>
-  <si>
-    <t>Alexandre Gleyson Araujo da Silva</t>
-  </si>
-  <si>
-    <t>R$ 63824.33</t>
-  </si>
-  <si>
-    <t>10/12/2026</t>
-  </si>
-  <si>
     <t>987 - MO VERA MOYSES - 04/09/26</t>
   </si>
   <si>
@@ -3279,24 +3291,21 @@
     <t>08/09/2026</t>
   </si>
   <si>
+    <t>561 - Samara Souza - 20/01/26</t>
+  </si>
+  <si>
+    <t>Tadeu Toledo Mathias</t>
+  </si>
+  <si>
+    <t>R$ 2932.99</t>
+  </si>
+  <si>
     <t>994 - Venda Avulsa - BRUNO RODRIGUES VASCONCELLOS</t>
   </si>
   <si>
     <t>15/11/2026</t>
   </si>
   <si>
-    <t>08/11/2026</t>
-  </si>
-  <si>
-    <t>561 - Samara Souza - 20/01/26</t>
-  </si>
-  <si>
-    <t>Tadeu Toledo Mathias</t>
-  </si>
-  <si>
-    <t>R$ 2932.99</t>
-  </si>
-  <si>
     <t>526 - Rafaela Ayres da Silva - 05/01/26</t>
   </si>
   <si>
@@ -4242,13 +4251,13 @@
     <t>Total Vendas</t>
   </si>
   <si>
-    <t>8881429,15</t>
+    <t>8871062,74</t>
   </si>
   <si>
     <t>Índice Médio</t>
   </si>
   <si>
-    <t>1,4178</t>
+    <t>1,4174</t>
   </si>
 </sst>
 </file>
@@ -4314,7 +4323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:K429"/>
+  <dimension ref="A2:K430"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.296875" customWidth="true" bestFit="true"/>
@@ -13291,34 +13300,34 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>102501.0</v>
+        <v>101701.0</v>
       </c>
       <c r="B276" t="s">
         <v>946</v>
       </c>
       <c r="C276" t="s">
-        <v>155</v>
+        <v>947</v>
       </c>
       <c r="D276" t="s">
-        <v>49</v>
+        <v>852</v>
       </c>
       <c r="E276" t="s">
-        <v>49</v>
+        <v>852</v>
       </c>
       <c r="F276" t="s">
         <v>36</v>
       </c>
       <c r="G276" t="s">
-        <v>247</v>
+        <v>65</v>
       </c>
       <c r="H276" t="s">
         <v>38</v>
       </c>
       <c r="I276" t="s">
-        <v>716</v>
+        <v>776</v>
       </c>
       <c r="J276" t="s">
-        <v>826</v>
+        <v>948</v>
       </c>
       <c r="K276" t="s">
         <v>2</v>
@@ -13326,34 +13335,34 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>102401.0</v>
+        <v>102501.0</v>
       </c>
       <c r="B277" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C277" t="s">
-        <v>948</v>
+        <v>155</v>
       </c>
       <c r="D277" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E277" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F277" t="s">
         <v>36</v>
       </c>
       <c r="G277" t="s">
-        <v>949</v>
+        <v>247</v>
       </c>
       <c r="H277" t="s">
         <v>38</v>
       </c>
       <c r="I277" t="s">
-        <v>860</v>
+        <v>716</v>
       </c>
       <c r="J277" t="s">
-        <v>853</v>
+        <v>826</v>
       </c>
       <c r="K277" t="s">
         <v>2</v>
@@ -13361,7 +13370,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>101101.0</v>
+        <v>102401.0</v>
       </c>
       <c r="B278" t="s">
         <v>950</v>
@@ -13370,25 +13379,25 @@
         <v>951</v>
       </c>
       <c r="D278" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E278" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="F278" t="s">
         <v>36</v>
       </c>
       <c r="G278" t="s">
-        <v>410</v>
+        <v>952</v>
       </c>
       <c r="H278" t="s">
         <v>38</v>
       </c>
       <c r="I278" t="s">
-        <v>791</v>
+        <v>860</v>
       </c>
       <c r="J278" t="s">
-        <v>200</v>
+        <v>853</v>
       </c>
       <c r="K278" t="s">
         <v>2</v>
@@ -13396,34 +13405,34 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>101701.0</v>
+        <v>102301.0</v>
       </c>
       <c r="B279" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C279" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D279" t="s">
-        <v>852</v>
+        <v>63</v>
       </c>
       <c r="E279" t="s">
-        <v>852</v>
+        <v>63</v>
       </c>
       <c r="F279" t="s">
         <v>36</v>
       </c>
       <c r="G279" t="s">
-        <v>65</v>
+        <v>435</v>
       </c>
       <c r="H279" t="s">
         <v>38</v>
       </c>
       <c r="I279" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="J279" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="K279" t="s">
         <v>2</v>
@@ -13431,25 +13440,25 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>102301.0</v>
+        <v>100901.0</v>
       </c>
       <c r="B280" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C280" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D280" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E280" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="F280" t="s">
         <v>36</v>
       </c>
       <c r="G280" t="s">
-        <v>435</v>
+        <v>958</v>
       </c>
       <c r="H280" t="s">
         <v>38</v>
@@ -13458,7 +13467,7 @@
         <v>772</v>
       </c>
       <c r="J280" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="K280" t="s">
         <v>2</v>
@@ -13466,34 +13475,34 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>100901.0</v>
+        <v>102901.0</v>
       </c>
       <c r="B281" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="C281" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="D281" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E281" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="F281" t="s">
         <v>36</v>
       </c>
       <c r="G281" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="H281" t="s">
         <v>38</v>
       </c>
       <c r="I281" t="s">
-        <v>772</v>
+        <v>963</v>
       </c>
       <c r="J281" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="K281" t="s">
         <v>2</v>
@@ -13501,13 +13510,13 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>100301.0</v>
+        <v>102101.0</v>
       </c>
       <c r="B282" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="C282" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="D282" t="s">
         <v>63</v>
@@ -13519,16 +13528,16 @@
         <v>36</v>
       </c>
       <c r="G282" t="s">
-        <v>964</v>
+        <v>435</v>
       </c>
       <c r="H282" t="s">
         <v>38</v>
       </c>
       <c r="I282" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="J282" t="s">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="K282" t="s">
         <v>2</v>
@@ -13536,34 +13545,34 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>97904.0</v>
+        <v>100301.0</v>
       </c>
       <c r="B283" t="s">
+        <v>968</v>
+      </c>
+      <c r="C283" t="s">
+        <v>969</v>
+      </c>
+      <c r="D283" t="s">
+        <v>63</v>
+      </c>
+      <c r="E283" t="s">
+        <v>63</v>
+      </c>
+      <c r="F283" t="s">
+        <v>36</v>
+      </c>
+      <c r="G283" t="s">
+        <v>970</v>
+      </c>
+      <c r="H283" t="s">
+        <v>38</v>
+      </c>
+      <c r="I283" t="s">
         <v>967</v>
       </c>
-      <c r="C283" t="s">
-        <v>948</v>
-      </c>
-      <c r="D283" t="s">
-        <v>35</v>
-      </c>
-      <c r="E283" t="s">
-        <v>35</v>
-      </c>
-      <c r="F283" t="s">
-        <v>36</v>
-      </c>
-      <c r="G283" t="s">
-        <v>949</v>
-      </c>
-      <c r="H283" t="s">
-        <v>52</v>
-      </c>
-      <c r="I283" t="s">
-        <v>768</v>
-      </c>
       <c r="J283" t="s">
-        <v>54</v>
+        <v>971</v>
       </c>
       <c r="K283" t="s">
         <v>2</v>
@@ -13571,13 +13580,13 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>101201.0</v>
+        <v>101101.0</v>
       </c>
       <c r="B284" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="C284" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="D284" t="s">
         <v>63</v>
@@ -13589,16 +13598,16 @@
         <v>36</v>
       </c>
       <c r="G284" t="s">
-        <v>970</v>
+        <v>410</v>
       </c>
       <c r="H284" t="s">
         <v>38</v>
       </c>
       <c r="I284" t="s">
-        <v>971</v>
+        <v>791</v>
       </c>
       <c r="J284" t="s">
-        <v>972</v>
+        <v>200</v>
       </c>
       <c r="K284" t="s">
         <v>2</v>
@@ -13606,34 +13615,34 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>102101.0</v>
+        <v>101801.0</v>
       </c>
       <c r="B285" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C285" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D285" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E285" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="F285" t="s">
         <v>36</v>
       </c>
       <c r="G285" t="s">
-        <v>435</v>
+        <v>976</v>
       </c>
       <c r="H285" t="s">
         <v>38</v>
       </c>
       <c r="I285" t="s">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="J285" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="K285" t="s">
         <v>2</v>
@@ -13641,34 +13650,34 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>101801.0</v>
+        <v>101201.0</v>
       </c>
       <c r="B286" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="C286" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="D286" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E286" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F286" t="s">
         <v>36</v>
       </c>
       <c r="G286" t="s">
+        <v>980</v>
+      </c>
+      <c r="H286" t="s">
+        <v>38</v>
+      </c>
+      <c r="I286" t="s">
         <v>977</v>
       </c>
-      <c r="H286" t="s">
-        <v>38</v>
-      </c>
-      <c r="I286" t="s">
-        <v>971</v>
-      </c>
       <c r="J286" t="s">
-        <v>957</v>
+        <v>981</v>
       </c>
       <c r="K286" t="s">
         <v>2</v>
@@ -13676,34 +13685,34 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>100501.0</v>
+        <v>97904.0</v>
       </c>
       <c r="B287" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="C287" t="s">
-        <v>979</v>
+        <v>951</v>
       </c>
       <c r="D287" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E287" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="F287" t="s">
         <v>36</v>
       </c>
       <c r="G287" t="s">
-        <v>980</v>
+        <v>952</v>
       </c>
       <c r="H287" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I287" t="s">
-        <v>981</v>
+        <v>768</v>
       </c>
       <c r="J287" t="s">
-        <v>957</v>
+        <v>54</v>
       </c>
       <c r="K287" t="s">
         <v>2</v>
@@ -13711,19 +13720,19 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>104401.0</v>
+        <v>105701.0</v>
       </c>
       <c r="B288" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C288" t="s">
-        <v>983</v>
+        <v>328</v>
       </c>
       <c r="D288" t="s">
-        <v>852</v>
+        <v>63</v>
       </c>
       <c r="E288" t="s">
-        <v>852</v>
+        <v>63</v>
       </c>
       <c r="F288" t="s">
         <v>36</v>
@@ -13738,7 +13747,7 @@
         <v>985</v>
       </c>
       <c r="J288" t="s">
-        <v>200</v>
+        <v>981</v>
       </c>
       <c r="K288" t="s">
         <v>2</v>
@@ -13746,7 +13755,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>105101.0</v>
+        <v>104401.0</v>
       </c>
       <c r="B289" t="s">
         <v>986</v>
@@ -13755,25 +13764,25 @@
         <v>987</v>
       </c>
       <c r="D289" t="s">
-        <v>63</v>
+        <v>852</v>
       </c>
       <c r="E289" t="s">
-        <v>63</v>
+        <v>852</v>
       </c>
       <c r="F289" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="G289" t="s">
         <v>988</v>
       </c>
       <c r="H289" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I289" t="s">
-        <v>901</v>
+        <v>989</v>
       </c>
       <c r="J289" t="s">
-        <v>989</v>
+        <v>54</v>
       </c>
       <c r="K289" t="s">
         <v>2</v>
@@ -13781,25 +13790,25 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>105301.0</v>
+        <v>105101.0</v>
       </c>
       <c r="B290" t="s">
         <v>990</v>
       </c>
       <c r="C290" t="s">
-        <v>930</v>
+        <v>991</v>
       </c>
       <c r="D290" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E290" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F290" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G290" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H290" t="s">
         <v>38</v>
@@ -13808,7 +13817,7 @@
         <v>901</v>
       </c>
       <c r="J290" t="s">
-        <v>99</v>
+        <v>993</v>
       </c>
       <c r="K290" t="s">
         <v>2</v>
@@ -13816,34 +13825,34 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>105701.0</v>
+        <v>105501.0</v>
       </c>
       <c r="B291" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="C291" t="s">
-        <v>328</v>
+        <v>995</v>
       </c>
       <c r="D291" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E291" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="F291" t="s">
         <v>36</v>
       </c>
       <c r="G291" t="s">
-        <v>993</v>
+        <v>511</v>
       </c>
       <c r="H291" t="s">
         <v>38</v>
       </c>
       <c r="I291" t="s">
-        <v>994</v>
+        <v>985</v>
       </c>
       <c r="J291" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="K291" t="s">
         <v>2</v>
@@ -13851,34 +13860,34 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>105501.0</v>
+        <v>106001.0</v>
       </c>
       <c r="B292" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C292" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="D292" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E292" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F292" t="s">
         <v>36</v>
       </c>
       <c r="G292" t="s">
-        <v>511</v>
+        <v>998</v>
       </c>
       <c r="H292" t="s">
         <v>38</v>
       </c>
       <c r="I292" t="s">
-        <v>994</v>
+        <v>764</v>
       </c>
       <c r="J292" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="K292" t="s">
         <v>2</v>
@@ -13886,34 +13895,34 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>102901.0</v>
+        <v>103501.0</v>
       </c>
       <c r="B293" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C293" t="s">
-        <v>999</v>
+        <v>651</v>
       </c>
       <c r="D293" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="E293" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="F293" t="s">
         <v>36</v>
       </c>
       <c r="G293" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H293" t="s">
         <v>38</v>
       </c>
       <c r="I293" t="s">
-        <v>1001</v>
+        <v>963</v>
       </c>
       <c r="J293" t="s">
-        <v>1002</v>
+        <v>964</v>
       </c>
       <c r="K293" t="s">
         <v>2</v>
@@ -13921,34 +13930,34 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>103801.0</v>
+        <v>104701.0</v>
       </c>
       <c r="B294" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C294" t="s">
+        <v>788</v>
+      </c>
+      <c r="D294" t="s">
+        <v>63</v>
+      </c>
+      <c r="E294" t="s">
+        <v>873</v>
+      </c>
+      <c r="F294" t="s">
+        <v>36</v>
+      </c>
+      <c r="G294" t="s">
         <v>1003</v>
       </c>
-      <c r="C294" t="s">
+      <c r="H294" t="s">
+        <v>38</v>
+      </c>
+      <c r="I294" t="s">
         <v>1004</v>
       </c>
-      <c r="D294" t="s">
-        <v>115</v>
-      </c>
-      <c r="E294" t="s">
-        <v>115</v>
-      </c>
-      <c r="F294" t="s">
-        <v>36</v>
-      </c>
-      <c r="G294" t="s">
+      <c r="J294" t="s">
         <v>1005</v>
-      </c>
-      <c r="H294" t="s">
-        <v>38</v>
-      </c>
-      <c r="I294" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J294" t="s">
-        <v>1007</v>
       </c>
       <c r="K294" t="s">
         <v>2</v>
@@ -13956,34 +13965,34 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>103501.0</v>
+        <v>103801.0</v>
       </c>
       <c r="B295" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C295" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D295" t="s">
+        <v>115</v>
+      </c>
+      <c r="E295" t="s">
+        <v>115</v>
+      </c>
+      <c r="F295" t="s">
+        <v>36</v>
+      </c>
+      <c r="G295" t="s">
         <v>1008</v>
       </c>
-      <c r="C295" t="s">
-        <v>651</v>
-      </c>
-      <c r="D295" t="s">
-        <v>150</v>
-      </c>
-      <c r="E295" t="s">
-        <v>150</v>
-      </c>
-      <c r="F295" t="s">
-        <v>36</v>
-      </c>
-      <c r="G295" t="s">
-        <v>1009</v>
-      </c>
       <c r="H295" t="s">
         <v>38</v>
       </c>
       <c r="I295" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="J295" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="K295" t="s">
         <v>2</v>
@@ -13991,34 +14000,34 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>105001.0</v>
+        <v>105301.0</v>
       </c>
       <c r="B296" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C296" t="s">
+        <v>930</v>
+      </c>
+      <c r="D296" t="s">
+        <v>49</v>
+      </c>
+      <c r="E296" t="s">
+        <v>49</v>
+      </c>
+      <c r="F296" t="s">
+        <v>36</v>
+      </c>
+      <c r="G296" t="s">
         <v>1010</v>
       </c>
-      <c r="C296" t="s">
-        <v>921</v>
-      </c>
-      <c r="D296" t="s">
-        <v>35</v>
-      </c>
-      <c r="E296" t="s">
-        <v>35</v>
-      </c>
-      <c r="F296" t="s">
-        <v>36</v>
-      </c>
-      <c r="G296" t="s">
-        <v>1011</v>
-      </c>
       <c r="H296" t="s">
         <v>38</v>
       </c>
       <c r="I296" t="s">
-        <v>1012</v>
+        <v>901</v>
       </c>
       <c r="J296" t="s">
-        <v>826</v>
+        <v>99</v>
       </c>
       <c r="K296" t="s">
         <v>2</v>
@@ -14026,10 +14035,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>79203.0</v>
+        <v>105001.0</v>
       </c>
       <c r="B297" t="s">
-        <v>920</v>
+        <v>1011</v>
       </c>
       <c r="C297" t="s">
         <v>921</v>
@@ -14041,19 +14050,19 @@
         <v>35</v>
       </c>
       <c r="F297" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="G297" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H297" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I297" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="J297" t="s">
-        <v>54</v>
+        <v>826</v>
       </c>
       <c r="K297" t="s">
         <v>2</v>
@@ -14061,34 +14070,34 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>104701.0</v>
+        <v>104801.0</v>
       </c>
       <c r="B298" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C298" t="s">
-        <v>788</v>
+        <v>1015</v>
       </c>
       <c r="D298" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E298" t="s">
-        <v>873</v>
+        <v>64</v>
       </c>
       <c r="F298" t="s">
         <v>36</v>
       </c>
       <c r="G298" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="H298" t="s">
         <v>38</v>
       </c>
       <c r="I298" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="J298" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="K298" t="s">
         <v>2</v>
@@ -14096,34 +14105,34 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>104801.0</v>
+        <v>79203.0</v>
       </c>
       <c r="B299" t="s">
-        <v>1015</v>
+        <v>920</v>
       </c>
       <c r="C299" t="s">
-        <v>1016</v>
+        <v>921</v>
       </c>
       <c r="D299" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="E299" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F299" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G299" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="H299" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I299" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="J299" t="s">
-        <v>1007</v>
+        <v>54</v>
       </c>
       <c r="K299" t="s">
         <v>2</v>
@@ -14134,7 +14143,7 @@
         <v>94301.0</v>
       </c>
       <c r="B300" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C300" t="s">
         <v>882</v>
@@ -14155,10 +14164,10 @@
         <v>38</v>
       </c>
       <c r="I300" t="s">
+        <v>1018</v>
+      </c>
+      <c r="J300" t="s">
         <v>1019</v>
-      </c>
-      <c r="J300" t="s">
-        <v>1020</v>
       </c>
       <c r="K300" t="s">
         <v>2</v>
@@ -14166,34 +14175,34 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>96801.0</v>
+        <v>97301.0</v>
       </c>
       <c r="B301" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C301" t="s">
+        <v>851</v>
+      </c>
+      <c r="D301" t="s">
+        <v>115</v>
+      </c>
+      <c r="E301" t="s">
+        <v>115</v>
+      </c>
+      <c r="F301" t="s">
+        <v>36</v>
+      </c>
+      <c r="G301" t="s">
         <v>1021</v>
       </c>
-      <c r="C301" t="s">
-        <v>198</v>
-      </c>
-      <c r="D301" t="s">
-        <v>63</v>
-      </c>
-      <c r="E301" t="s">
-        <v>64</v>
-      </c>
-      <c r="F301" t="s">
-        <v>36</v>
-      </c>
-      <c r="G301" t="s">
+      <c r="H301" t="s">
+        <v>38</v>
+      </c>
+      <c r="I301" t="s">
+        <v>867</v>
+      </c>
+      <c r="J301" t="s">
         <v>1022</v>
-      </c>
-      <c r="H301" t="s">
-        <v>38</v>
-      </c>
-      <c r="I301" t="s">
-        <v>1023</v>
-      </c>
-      <c r="J301" t="s">
-        <v>1024</v>
       </c>
       <c r="K301" t="s">
         <v>2</v>
@@ -14201,16 +14210,16 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>96401.0</v>
+        <v>96801.0</v>
       </c>
       <c r="B302" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C302" t="s">
-        <v>799</v>
+        <v>198</v>
       </c>
       <c r="D302" t="s">
-        <v>800</v>
+        <v>63</v>
       </c>
       <c r="E302" t="s">
         <v>64</v>
@@ -14219,16 +14228,16 @@
         <v>36</v>
       </c>
       <c r="G302" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H302" t="s">
+        <v>38</v>
+      </c>
+      <c r="I302" t="s">
+        <v>1025</v>
+      </c>
+      <c r="J302" t="s">
         <v>1026</v>
-      </c>
-      <c r="H302" t="s">
-        <v>38</v>
-      </c>
-      <c r="I302" t="s">
-        <v>1027</v>
-      </c>
-      <c r="J302" t="s">
-        <v>1028</v>
       </c>
       <c r="K302" t="s">
         <v>2</v>
@@ -14236,34 +14245,34 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>95301.0</v>
+        <v>96401.0</v>
       </c>
       <c r="B303" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C303" t="s">
+        <v>799</v>
+      </c>
+      <c r="D303" t="s">
+        <v>800</v>
+      </c>
+      <c r="E303" t="s">
+        <v>64</v>
+      </c>
+      <c r="F303" t="s">
+        <v>36</v>
+      </c>
+      <c r="G303" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H303" t="s">
+        <v>38</v>
+      </c>
+      <c r="I303" t="s">
         <v>1029</v>
       </c>
-      <c r="C303" t="s">
+      <c r="J303" t="s">
         <v>1030</v>
-      </c>
-      <c r="D303" t="s">
-        <v>150</v>
-      </c>
-      <c r="E303" t="s">
-        <v>150</v>
-      </c>
-      <c r="F303" t="s">
-        <v>36</v>
-      </c>
-      <c r="G303" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H303" t="s">
-        <v>38</v>
-      </c>
-      <c r="I303" t="s">
-        <v>1032</v>
-      </c>
-      <c r="J303" t="s">
-        <v>1033</v>
       </c>
       <c r="K303" t="s">
         <v>2</v>
@@ -14271,25 +14280,25 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>97301.0</v>
+        <v>96101.0</v>
       </c>
       <c r="B304" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="C304" t="s">
-        <v>851</v>
+        <v>1007</v>
       </c>
       <c r="D304" t="s">
-        <v>115</v>
+        <v>852</v>
       </c>
       <c r="E304" t="s">
-        <v>115</v>
+        <v>852</v>
       </c>
       <c r="F304" t="s">
         <v>36</v>
       </c>
       <c r="G304" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="H304" t="s">
         <v>38</v>
@@ -14298,7 +14307,7 @@
         <v>867</v>
       </c>
       <c r="J304" t="s">
-        <v>1036</v>
+        <v>853</v>
       </c>
       <c r="K304" t="s">
         <v>2</v>
@@ -14306,34 +14315,34 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>96101.0</v>
+        <v>94901.0</v>
       </c>
       <c r="B305" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C305" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D305" t="s">
+        <v>35</v>
+      </c>
+      <c r="E305" t="s">
+        <v>35</v>
+      </c>
+      <c r="F305" t="s">
+        <v>36</v>
+      </c>
+      <c r="G305" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H305" t="s">
+        <v>38</v>
+      </c>
+      <c r="I305" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J305" t="s">
         <v>1037</v>
-      </c>
-      <c r="C305" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D305" t="s">
-        <v>852</v>
-      </c>
-      <c r="E305" t="s">
-        <v>852</v>
-      </c>
-      <c r="F305" t="s">
-        <v>36</v>
-      </c>
-      <c r="G305" t="s">
-        <v>1038</v>
-      </c>
-      <c r="H305" t="s">
-        <v>38</v>
-      </c>
-      <c r="I305" t="s">
-        <v>867</v>
-      </c>
-      <c r="J305" t="s">
-        <v>853</v>
       </c>
       <c r="K305" t="s">
         <v>2</v>
@@ -14341,13 +14350,13 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>94901.0</v>
+        <v>96501.0</v>
       </c>
       <c r="B306" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C306" t="s">
         <v>1039</v>
-      </c>
-      <c r="C306" t="s">
-        <v>1040</v>
       </c>
       <c r="D306" t="s">
         <v>35</v>
@@ -14356,19 +14365,19 @@
         <v>35</v>
       </c>
       <c r="F306" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G306" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H306" t="s">
+        <v>38</v>
+      </c>
+      <c r="I306" t="s">
         <v>1041</v>
       </c>
-      <c r="H306" t="s">
-        <v>38</v>
-      </c>
-      <c r="I306" t="s">
+      <c r="J306" t="s">
         <v>1042</v>
-      </c>
-      <c r="J306" t="s">
-        <v>1043</v>
       </c>
       <c r="K306" t="s">
         <v>2</v>
@@ -14379,7 +14388,7 @@
         <v>93401.0</v>
       </c>
       <c r="B307" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C307" t="s">
         <v>862</v>
@@ -14394,16 +14403,16 @@
         <v>36</v>
       </c>
       <c r="G307" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H307" t="s">
         <v>38</v>
       </c>
       <c r="I307" t="s">
+        <v>1018</v>
+      </c>
+      <c r="J307" t="s">
         <v>1019</v>
-      </c>
-      <c r="J307" t="s">
-        <v>1020</v>
       </c>
       <c r="K307" t="s">
         <v>2</v>
@@ -14414,10 +14423,10 @@
         <v>92301.0</v>
       </c>
       <c r="B308" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C308" t="s">
         <v>1046</v>
-      </c>
-      <c r="C308" t="s">
-        <v>1047</v>
       </c>
       <c r="D308" t="s">
         <v>63</v>
@@ -14435,7 +14444,7 @@
         <v>38</v>
       </c>
       <c r="I308" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="J308" t="s">
         <v>586</v>
@@ -14446,34 +14455,34 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>95001.0</v>
+        <v>95301.0</v>
       </c>
       <c r="B309" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C309" t="s">
         <v>1048</v>
       </c>
-      <c r="C309" t="s">
+      <c r="D309" t="s">
+        <v>150</v>
+      </c>
+      <c r="E309" t="s">
+        <v>150</v>
+      </c>
+      <c r="F309" t="s">
+        <v>36</v>
+      </c>
+      <c r="G309" t="s">
         <v>1049</v>
       </c>
-      <c r="D309" t="s">
-        <v>49</v>
-      </c>
-      <c r="E309" t="s">
-        <v>49</v>
-      </c>
-      <c r="F309" t="s">
-        <v>36</v>
-      </c>
-      <c r="G309" t="s">
-        <v>105</v>
-      </c>
       <c r="H309" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I309" t="s">
         <v>1050</v>
       </c>
       <c r="J309" t="s">
-        <v>54</v>
+        <v>1051</v>
       </c>
       <c r="K309" t="s">
         <v>2</v>
@@ -14481,31 +14490,31 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>91901.0</v>
+        <v>95001.0</v>
       </c>
       <c r="B310" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C310" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D310" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E310" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="F310" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="G310" t="s">
-        <v>1053</v>
+        <v>105</v>
       </c>
       <c r="H310" t="s">
         <v>52</v>
       </c>
       <c r="I310" t="s">
-        <v>879</v>
+        <v>1054</v>
       </c>
       <c r="J310" t="s">
         <v>54</v>
@@ -14516,13 +14525,13 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>94401.0</v>
+        <v>91901.0</v>
       </c>
       <c r="B311" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C311" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="D311" t="s">
         <v>63</v>
@@ -14531,19 +14540,19 @@
         <v>63</v>
       </c>
       <c r="F311" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G311" t="s">
-        <v>648</v>
+        <v>1057</v>
       </c>
       <c r="H311" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I311" t="s">
-        <v>1056</v>
+        <v>879</v>
       </c>
       <c r="J311" t="s">
-        <v>826</v>
+        <v>54</v>
       </c>
       <c r="K311" t="s">
         <v>2</v>
@@ -14551,34 +14560,34 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>101401.0</v>
+        <v>94401.0</v>
       </c>
       <c r="B312" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C312" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D312" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E312" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F312" t="s">
         <v>36</v>
       </c>
       <c r="G312" t="s">
-        <v>1059</v>
+        <v>648</v>
       </c>
       <c r="H312" t="s">
         <v>38</v>
       </c>
       <c r="I312" t="s">
-        <v>915</v>
+        <v>1060</v>
       </c>
       <c r="J312" t="s">
-        <v>957</v>
+        <v>826</v>
       </c>
       <c r="K312" t="s">
         <v>2</v>
@@ -14586,13 +14595,13 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>96901.0</v>
+        <v>100501.0</v>
       </c>
       <c r="B313" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C313" t="s">
-        <v>328</v>
+        <v>1062</v>
       </c>
       <c r="D313" t="s">
         <v>63</v>
@@ -14604,16 +14613,16 @@
         <v>36</v>
       </c>
       <c r="G313" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="H313" t="s">
         <v>38</v>
       </c>
       <c r="I313" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="J313" t="s">
-        <v>586</v>
+        <v>955</v>
       </c>
       <c r="K313" t="s">
         <v>2</v>
@@ -14621,34 +14630,34 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>95401.0</v>
+        <v>97903.0</v>
       </c>
       <c r="B314" t="s">
-        <v>1063</v>
+        <v>982</v>
       </c>
       <c r="C314" t="s">
-        <v>1064</v>
+        <v>951</v>
       </c>
       <c r="D314" t="s">
-        <v>852</v>
+        <v>35</v>
       </c>
       <c r="E314" t="s">
-        <v>852</v>
+        <v>35</v>
       </c>
       <c r="F314" t="s">
         <v>36</v>
       </c>
       <c r="G314" t="s">
-        <v>1065</v>
+        <v>488</v>
       </c>
       <c r="H314" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I314" t="s">
-        <v>1066</v>
+        <v>173</v>
       </c>
       <c r="J314" t="s">
-        <v>586</v>
+        <v>54</v>
       </c>
       <c r="K314" t="s">
         <v>2</v>
@@ -14656,34 +14665,34 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>95701.0</v>
+        <v>96901.0</v>
       </c>
       <c r="B315" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C315" t="s">
+        <v>328</v>
+      </c>
+      <c r="D315" t="s">
+        <v>63</v>
+      </c>
+      <c r="E315" t="s">
+        <v>63</v>
+      </c>
+      <c r="F315" t="s">
+        <v>36</v>
+      </c>
+      <c r="G315" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H315" t="s">
+        <v>38</v>
+      </c>
+      <c r="I315" t="s">
         <v>1067</v>
       </c>
-      <c r="C315" t="s">
-        <v>180</v>
-      </c>
-      <c r="D315" t="s">
-        <v>49</v>
-      </c>
-      <c r="E315" t="s">
-        <v>49</v>
-      </c>
-      <c r="F315" t="s">
-        <v>36</v>
-      </c>
-      <c r="G315" t="s">
-        <v>1068</v>
-      </c>
-      <c r="H315" t="s">
-        <v>38</v>
-      </c>
-      <c r="I315" t="s">
-        <v>1066</v>
-      </c>
       <c r="J315" t="s">
-        <v>1069</v>
+        <v>586</v>
       </c>
       <c r="K315" t="s">
         <v>2</v>
@@ -14691,34 +14700,34 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>97903.0</v>
+        <v>95401.0</v>
       </c>
       <c r="B316" t="s">
-        <v>967</v>
+        <v>1068</v>
       </c>
       <c r="C316" t="s">
-        <v>948</v>
+        <v>1069</v>
       </c>
       <c r="D316" t="s">
-        <v>35</v>
+        <v>852</v>
       </c>
       <c r="E316" t="s">
-        <v>35</v>
+        <v>852</v>
       </c>
       <c r="F316" t="s">
         <v>36</v>
       </c>
       <c r="G316" t="s">
-        <v>488</v>
+        <v>1070</v>
       </c>
       <c r="H316" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I316" t="s">
-        <v>173</v>
+        <v>1071</v>
       </c>
       <c r="J316" t="s">
-        <v>54</v>
+        <v>586</v>
       </c>
       <c r="K316" t="s">
         <v>2</v>
@@ -14729,10 +14738,10 @@
         <v>96601.0</v>
       </c>
       <c r="B317" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="C317" t="s">
-        <v>1058</v>
+        <v>1073</v>
       </c>
       <c r="D317" t="s">
         <v>35</v>
@@ -14744,7 +14753,7 @@
         <v>36</v>
       </c>
       <c r="G317" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="H317" t="s">
         <v>38</v>
@@ -14753,7 +14762,7 @@
         <v>915</v>
       </c>
       <c r="J317" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="K317" t="s">
         <v>2</v>
@@ -14761,13 +14770,13 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>96501.0</v>
+        <v>101401.0</v>
       </c>
       <c r="B318" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C318" t="s">
         <v>1073</v>
-      </c>
-      <c r="C318" t="s">
-        <v>1074</v>
       </c>
       <c r="D318" t="s">
         <v>35</v>
@@ -14776,19 +14785,19 @@
         <v>35</v>
       </c>
       <c r="F318" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="G318" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="H318" t="s">
         <v>38</v>
       </c>
       <c r="I318" t="s">
-        <v>1076</v>
+        <v>915</v>
       </c>
       <c r="J318" t="s">
-        <v>1077</v>
+        <v>955</v>
       </c>
       <c r="K318" t="s">
         <v>2</v>
@@ -14796,7 +14805,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>97601.0</v>
+        <v>97401.0</v>
       </c>
       <c r="B319" t="s">
         <v>1078</v>
@@ -14805,10 +14814,10 @@
         <v>1079</v>
       </c>
       <c r="D319" t="s">
-        <v>852</v>
+        <v>35</v>
       </c>
       <c r="E319" t="s">
-        <v>852</v>
+        <v>35</v>
       </c>
       <c r="F319" t="s">
         <v>36</v>
@@ -14820,10 +14829,10 @@
         <v>38</v>
       </c>
       <c r="I319" t="s">
-        <v>1076</v>
+        <v>1041</v>
       </c>
       <c r="J319" t="s">
-        <v>853</v>
+        <v>1081</v>
       </c>
       <c r="K319" t="s">
         <v>2</v>
@@ -14831,13 +14840,13 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>97401.0</v>
+        <v>97901.0</v>
       </c>
       <c r="B320" t="s">
-        <v>1081</v>
+        <v>982</v>
       </c>
       <c r="C320" t="s">
-        <v>1082</v>
+        <v>951</v>
       </c>
       <c r="D320" t="s">
         <v>35</v>
@@ -14849,16 +14858,16 @@
         <v>36</v>
       </c>
       <c r="G320" t="s">
-        <v>1083</v>
+        <v>65</v>
       </c>
       <c r="H320" t="s">
         <v>38</v>
       </c>
       <c r="I320" t="s">
-        <v>1076</v>
+        <v>1030</v>
       </c>
       <c r="J320" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="K320" t="s">
         <v>2</v>
@@ -14866,13 +14875,13 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>98701.0</v>
+        <v>97601.0</v>
       </c>
       <c r="B321" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="C321" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="D321" t="s">
         <v>852</v>
@@ -14884,16 +14893,16 @@
         <v>36</v>
       </c>
       <c r="G321" t="s">
-        <v>65</v>
+        <v>1085</v>
       </c>
       <c r="H321" t="s">
         <v>38</v>
       </c>
       <c r="I321" t="s">
-        <v>1087</v>
+        <v>1041</v>
       </c>
       <c r="J321" t="s">
-        <v>896</v>
+        <v>853</v>
       </c>
       <c r="K321" t="s">
         <v>2</v>
@@ -14901,34 +14910,34 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>99401.0</v>
+        <v>95701.0</v>
       </c>
       <c r="B322" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C322" t="s">
+        <v>180</v>
+      </c>
+      <c r="D322" t="s">
+        <v>49</v>
+      </c>
+      <c r="E322" t="s">
+        <v>49</v>
+      </c>
+      <c r="F322" t="s">
+        <v>36</v>
+      </c>
+      <c r="G322" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H322" t="s">
+        <v>38</v>
+      </c>
+      <c r="I322" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J322" t="s">
         <v>1088</v>
-      </c>
-      <c r="C322" t="s">
-        <v>778</v>
-      </c>
-      <c r="D322" t="s">
-        <v>63</v>
-      </c>
-      <c r="E322" t="s">
-        <v>63</v>
-      </c>
-      <c r="F322" t="s">
-        <v>36</v>
-      </c>
-      <c r="G322" t="s">
-        <v>65</v>
-      </c>
-      <c r="H322" t="s">
-        <v>38</v>
-      </c>
-      <c r="I322" t="s">
-        <v>1087</v>
-      </c>
-      <c r="J322" t="s">
-        <v>1089</v>
       </c>
       <c r="K322" t="s">
         <v>2</v>
@@ -14936,19 +14945,19 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>97901.0</v>
+        <v>98701.0</v>
       </c>
       <c r="B323" t="s">
-        <v>967</v>
+        <v>1089</v>
       </c>
       <c r="C323" t="s">
-        <v>948</v>
+        <v>1090</v>
       </c>
       <c r="D323" t="s">
-        <v>35</v>
+        <v>852</v>
       </c>
       <c r="E323" t="s">
-        <v>35</v>
+        <v>852</v>
       </c>
       <c r="F323" t="s">
         <v>36</v>
@@ -14960,10 +14969,10 @@
         <v>38</v>
       </c>
       <c r="I323" t="s">
-        <v>1028</v>
+        <v>1091</v>
       </c>
       <c r="J323" t="s">
-        <v>1090</v>
+        <v>896</v>
       </c>
       <c r="K323" t="s">
         <v>2</v>
@@ -14974,10 +14983,10 @@
         <v>56102.0</v>
       </c>
       <c r="B324" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C324" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D324" t="s">
         <v>35</v>
@@ -14989,13 +14998,13 @@
         <v>36</v>
       </c>
       <c r="G324" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H324" t="s">
         <v>38</v>
       </c>
       <c r="I324" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="J324" t="s">
         <v>896</v>
@@ -15006,34 +15015,34 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>52601.0</v>
+        <v>99401.0</v>
       </c>
       <c r="B325" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C325" t="s">
-        <v>1095</v>
+        <v>778</v>
       </c>
       <c r="D325" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E325" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F325" t="s">
         <v>36</v>
       </c>
       <c r="G325" t="s">
+        <v>65</v>
+      </c>
+      <c r="H325" t="s">
+        <v>38</v>
+      </c>
+      <c r="I325" t="s">
+        <v>1091</v>
+      </c>
+      <c r="J325" t="s">
         <v>1096</v>
-      </c>
-      <c r="H325" t="s">
-        <v>38</v>
-      </c>
-      <c r="I325" t="s">
-        <v>132</v>
-      </c>
-      <c r="J325" t="s">
-        <v>1097</v>
       </c>
       <c r="K325" t="s">
         <v>2</v>
@@ -15041,13 +15050,13 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>64401.0</v>
+        <v>52601.0</v>
       </c>
       <c r="B326" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C326" t="s">
         <v>1098</v>
-      </c>
-      <c r="C326" t="s">
-        <v>1099</v>
       </c>
       <c r="D326" t="s">
         <v>35</v>
@@ -15059,16 +15068,16 @@
         <v>36</v>
       </c>
       <c r="G326" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H326" t="s">
+        <v>38</v>
+      </c>
+      <c r="I326" t="s">
+        <v>132</v>
+      </c>
+      <c r="J326" t="s">
         <v>1100</v>
-      </c>
-      <c r="H326" t="s">
-        <v>38</v>
-      </c>
-      <c r="I326" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J326" t="s">
-        <v>1102</v>
       </c>
       <c r="K326" t="s">
         <v>2</v>
@@ -15076,34 +15085,34 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>64002.0</v>
+        <v>64401.0</v>
       </c>
       <c r="B327" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C327" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D327" t="s">
+        <v>35</v>
+      </c>
+      <c r="E327" t="s">
+        <v>35</v>
+      </c>
+      <c r="F327" t="s">
+        <v>36</v>
+      </c>
+      <c r="G327" t="s">
         <v>1103</v>
       </c>
-      <c r="C327" t="s">
+      <c r="H327" t="s">
+        <v>38</v>
+      </c>
+      <c r="I327" t="s">
         <v>1104</v>
       </c>
-      <c r="D327" t="s">
-        <v>64</v>
-      </c>
-      <c r="E327" t="s">
-        <v>64</v>
-      </c>
-      <c r="F327" t="s">
-        <v>36</v>
-      </c>
-      <c r="G327" t="s">
+      <c r="J327" t="s">
         <v>1105</v>
-      </c>
-      <c r="H327" t="s">
-        <v>38</v>
-      </c>
-      <c r="I327" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J327" t="s">
-        <v>1106</v>
       </c>
       <c r="K327" t="s">
         <v>2</v>
@@ -15111,34 +15120,34 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>62701.0</v>
+        <v>64002.0</v>
       </c>
       <c r="B328" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C328" t="s">
         <v>1107</v>
       </c>
-      <c r="C328" t="s">
-        <v>848</v>
-      </c>
       <c r="D328" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E328" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F328" t="s">
         <v>36</v>
       </c>
       <c r="G328" t="s">
-        <v>771</v>
+        <v>1108</v>
       </c>
       <c r="H328" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I328" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="J328" t="s">
-        <v>54</v>
+        <v>1109</v>
       </c>
       <c r="K328" t="s">
         <v>2</v>
@@ -15146,34 +15155,34 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>63901.0</v>
+        <v>62701.0</v>
       </c>
       <c r="B329" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C329" t="s">
-        <v>1110</v>
+        <v>848</v>
       </c>
       <c r="D329" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E329" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F329" t="s">
         <v>36</v>
       </c>
       <c r="G329" t="s">
+        <v>771</v>
+      </c>
+      <c r="H329" t="s">
+        <v>52</v>
+      </c>
+      <c r="I329" t="s">
         <v>1111</v>
       </c>
-      <c r="H329" t="s">
-        <v>38</v>
-      </c>
-      <c r="I329" t="s">
-        <v>1101</v>
-      </c>
       <c r="J329" t="s">
-        <v>1102</v>
+        <v>54</v>
       </c>
       <c r="K329" t="s">
         <v>2</v>
@@ -15181,7 +15190,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>62901.0</v>
+        <v>63901.0</v>
       </c>
       <c r="B330" t="s">
         <v>1112</v>
@@ -15205,10 +15214,10 @@
         <v>38</v>
       </c>
       <c r="I330" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="J330" t="s">
-        <v>972</v>
+        <v>1105</v>
       </c>
       <c r="K330" t="s">
         <v>2</v>
@@ -15216,7 +15225,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>62801.0</v>
+        <v>62901.0</v>
       </c>
       <c r="B331" t="s">
         <v>1115</v>
@@ -15225,13 +15234,13 @@
         <v>1116</v>
       </c>
       <c r="D331" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E331" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="F331" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="G331" t="s">
         <v>1117</v>
@@ -15240,10 +15249,10 @@
         <v>38</v>
       </c>
       <c r="I331" t="s">
-        <v>1118</v>
+        <v>1104</v>
       </c>
       <c r="J331" t="s">
-        <v>1119</v>
+        <v>981</v>
       </c>
       <c r="K331" t="s">
         <v>2</v>
@@ -15251,13 +15260,13 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>51702.0</v>
+        <v>62801.0</v>
       </c>
       <c r="B332" t="s">
-        <v>327</v>
+        <v>1118</v>
       </c>
       <c r="C332" t="s">
-        <v>328</v>
+        <v>1119</v>
       </c>
       <c r="D332" t="s">
         <v>63</v>
@@ -15266,19 +15275,19 @@
         <v>63</v>
       </c>
       <c r="F332" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G332" t="s">
         <v>1120</v>
       </c>
       <c r="H332" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I332" t="s">
-        <v>407</v>
+        <v>1121</v>
       </c>
       <c r="J332" t="s">
-        <v>54</v>
+        <v>1122</v>
       </c>
       <c r="K332" t="s">
         <v>2</v>
@@ -15286,34 +15295,34 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>61001.0</v>
+        <v>51702.0</v>
       </c>
       <c r="B333" t="s">
-        <v>1121</v>
+        <v>327</v>
       </c>
       <c r="C333" t="s">
-        <v>1122</v>
+        <v>328</v>
       </c>
       <c r="D333" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E333" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F333" t="s">
         <v>36</v>
       </c>
       <c r="G333" t="s">
-        <v>279</v>
+        <v>1123</v>
       </c>
       <c r="H333" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I333" t="s">
-        <v>258</v>
+        <v>407</v>
       </c>
       <c r="J333" t="s">
-        <v>891</v>
+        <v>54</v>
       </c>
       <c r="K333" t="s">
         <v>2</v>
@@ -15321,34 +15330,34 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>63801.0</v>
+        <v>61001.0</v>
       </c>
       <c r="B334" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C334" t="s">
-        <v>290</v>
+        <v>1125</v>
       </c>
       <c r="D334" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E334" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="F334" t="s">
         <v>36</v>
       </c>
       <c r="G334" t="s">
-        <v>1124</v>
+        <v>279</v>
       </c>
       <c r="H334" t="s">
         <v>38</v>
       </c>
       <c r="I334" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="J334" t="s">
-        <v>580</v>
+        <v>891</v>
       </c>
       <c r="K334" t="s">
         <v>2</v>
@@ -15356,34 +15365,34 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>63401.0</v>
+        <v>63801.0</v>
       </c>
       <c r="B335" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C335" t="s">
-        <v>328</v>
+        <v>290</v>
       </c>
       <c r="D335" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E335" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="F335" t="s">
         <v>36</v>
       </c>
       <c r="G335" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H335" t="s">
         <v>38</v>
       </c>
       <c r="I335" t="s">
-        <v>407</v>
+        <v>255</v>
       </c>
       <c r="J335" t="s">
-        <v>1127</v>
+        <v>580</v>
       </c>
       <c r="K335" t="s">
         <v>2</v>
@@ -15391,25 +15400,25 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>62301.0</v>
+        <v>63401.0</v>
       </c>
       <c r="B336" t="s">
         <v>1128</v>
       </c>
       <c r="C336" t="s">
+        <v>328</v>
+      </c>
+      <c r="D336" t="s">
+        <v>63</v>
+      </c>
+      <c r="E336" t="s">
+        <v>63</v>
+      </c>
+      <c r="F336" t="s">
+        <v>36</v>
+      </c>
+      <c r="G336" t="s">
         <v>1129</v>
-      </c>
-      <c r="D336" t="s">
-        <v>63</v>
-      </c>
-      <c r="E336" t="s">
-        <v>63</v>
-      </c>
-      <c r="F336" t="s">
-        <v>1130</v>
-      </c>
-      <c r="G336" t="s">
-        <v>1131</v>
       </c>
       <c r="H336" t="s">
         <v>38</v>
@@ -15418,7 +15427,7 @@
         <v>407</v>
       </c>
       <c r="J336" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="K336" t="s">
         <v>2</v>
@@ -15426,34 +15435,34 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>61901.0</v>
+        <v>62301.0</v>
       </c>
       <c r="B337" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C337" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D337" t="s">
+        <v>63</v>
+      </c>
+      <c r="E337" t="s">
+        <v>63</v>
+      </c>
+      <c r="F337" t="s">
         <v>1133</v>
       </c>
-      <c r="C337" t="s">
+      <c r="G337" t="s">
         <v>1134</v>
       </c>
-      <c r="D337" t="s">
-        <v>49</v>
-      </c>
-      <c r="E337" t="s">
-        <v>49</v>
-      </c>
-      <c r="F337" t="s">
-        <v>36</v>
-      </c>
-      <c r="G337" t="s">
+      <c r="H337" t="s">
+        <v>38</v>
+      </c>
+      <c r="I337" t="s">
+        <v>407</v>
+      </c>
+      <c r="J337" t="s">
         <v>1135</v>
-      </c>
-      <c r="H337" t="s">
-        <v>38</v>
-      </c>
-      <c r="I337" t="s">
-        <v>258</v>
-      </c>
-      <c r="J337" t="s">
-        <v>1136</v>
       </c>
       <c r="K337" t="s">
         <v>2</v>
@@ -15461,34 +15470,34 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>66301.0</v>
+        <v>61901.0</v>
       </c>
       <c r="B338" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C338" t="s">
         <v>1137</v>
       </c>
-      <c r="C338" t="s">
+      <c r="D338" t="s">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>49</v>
+      </c>
+      <c r="F338" t="s">
+        <v>36</v>
+      </c>
+      <c r="G338" t="s">
         <v>1138</v>
       </c>
-      <c r="D338" t="s">
-        <v>49</v>
-      </c>
-      <c r="E338" t="s">
-        <v>49</v>
-      </c>
-      <c r="F338" t="s">
-        <v>36</v>
-      </c>
-      <c r="G338" t="s">
+      <c r="H338" t="s">
+        <v>38</v>
+      </c>
+      <c r="I338" t="s">
+        <v>258</v>
+      </c>
+      <c r="J338" t="s">
         <v>1139</v>
-      </c>
-      <c r="H338" t="s">
-        <v>38</v>
-      </c>
-      <c r="I338" t="s">
-        <v>1140</v>
-      </c>
-      <c r="J338" t="s">
-        <v>432</v>
       </c>
       <c r="K338" t="s">
         <v>2</v>
@@ -15496,25 +15505,25 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>64801.0</v>
+        <v>66301.0</v>
       </c>
       <c r="B339" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C339" t="s">
         <v>1141</v>
       </c>
-      <c r="C339" t="s">
+      <c r="D339" t="s">
+        <v>49</v>
+      </c>
+      <c r="E339" t="s">
+        <v>49</v>
+      </c>
+      <c r="F339" t="s">
+        <v>36</v>
+      </c>
+      <c r="G339" t="s">
         <v>1142</v>
-      </c>
-      <c r="D339" t="s">
-        <v>49</v>
-      </c>
-      <c r="E339" t="s">
-        <v>49</v>
-      </c>
-      <c r="F339" t="s">
-        <v>36</v>
-      </c>
-      <c r="G339" t="s">
-        <v>397</v>
       </c>
       <c r="H339" t="s">
         <v>38</v>
@@ -15523,7 +15532,7 @@
         <v>1143</v>
       </c>
       <c r="J339" t="s">
-        <v>1144</v>
+        <v>432</v>
       </c>
       <c r="K339" t="s">
         <v>2</v>
@@ -15531,34 +15540,34 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>68501.0</v>
+        <v>64801.0</v>
       </c>
       <c r="B340" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C340" t="s">
         <v>1145</v>
       </c>
-      <c r="C340" t="s">
+      <c r="D340" t="s">
+        <v>49</v>
+      </c>
+      <c r="E340" t="s">
+        <v>49</v>
+      </c>
+      <c r="F340" t="s">
+        <v>36</v>
+      </c>
+      <c r="G340" t="s">
+        <v>397</v>
+      </c>
+      <c r="H340" t="s">
+        <v>38</v>
+      </c>
+      <c r="I340" t="s">
         <v>1146</v>
       </c>
-      <c r="D340" t="s">
-        <v>49</v>
-      </c>
-      <c r="E340" t="s">
-        <v>49</v>
-      </c>
-      <c r="F340" t="s">
+      <c r="J340" t="s">
         <v>1147</v>
-      </c>
-      <c r="G340" t="s">
-        <v>1148</v>
-      </c>
-      <c r="H340" t="s">
-        <v>38</v>
-      </c>
-      <c r="I340" t="s">
-        <v>1143</v>
-      </c>
-      <c r="J340" t="s">
-        <v>1144</v>
       </c>
       <c r="K340" t="s">
         <v>2</v>
@@ -15566,34 +15575,34 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>67101.0</v>
+        <v>68501.0</v>
       </c>
       <c r="B341" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C341" t="s">
         <v>1149</v>
       </c>
-      <c r="C341" t="s">
+      <c r="D341" t="s">
+        <v>49</v>
+      </c>
+      <c r="E341" t="s">
+        <v>49</v>
+      </c>
+      <c r="F341" t="s">
         <v>1150</v>
-      </c>
-      <c r="D341" t="s">
-        <v>63</v>
-      </c>
-      <c r="E341" t="s">
-        <v>63</v>
-      </c>
-      <c r="F341" t="s">
-        <v>36</v>
       </c>
       <c r="G341" t="s">
         <v>1151</v>
       </c>
       <c r="H341" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I341" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="J341" t="s">
-        <v>54</v>
+        <v>1147</v>
       </c>
       <c r="K341" t="s">
         <v>2</v>
@@ -15601,34 +15610,34 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>68201.0</v>
+        <v>67101.0</v>
       </c>
       <c r="B342" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C342" t="s">
         <v>1153</v>
       </c>
-      <c r="C342" t="s">
+      <c r="D342" t="s">
+        <v>63</v>
+      </c>
+      <c r="E342" t="s">
+        <v>63</v>
+      </c>
+      <c r="F342" t="s">
+        <v>36</v>
+      </c>
+      <c r="G342" t="s">
         <v>1154</v>
       </c>
-      <c r="D342" t="s">
-        <v>49</v>
-      </c>
-      <c r="E342" t="s">
-        <v>49</v>
-      </c>
-      <c r="F342" t="s">
-        <v>124</v>
-      </c>
-      <c r="G342" t="s">
+      <c r="H342" t="s">
+        <v>52</v>
+      </c>
+      <c r="I342" t="s">
         <v>1155</v>
       </c>
-      <c r="H342" t="s">
-        <v>38</v>
-      </c>
-      <c r="I342" t="s">
-        <v>1156</v>
-      </c>
       <c r="J342" t="s">
-        <v>1157</v>
+        <v>54</v>
       </c>
       <c r="K342" t="s">
         <v>2</v>
@@ -15636,34 +15645,34 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>63501.0</v>
+        <v>68201.0</v>
       </c>
       <c r="B343" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C343" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="D343" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E343" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F343" t="s">
         <v>124</v>
       </c>
       <c r="G343" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H343" t="s">
+        <v>38</v>
+      </c>
+      <c r="I343" t="s">
+        <v>1159</v>
+      </c>
+      <c r="J343" t="s">
         <v>1160</v>
-      </c>
-      <c r="H343" t="s">
-        <v>38</v>
-      </c>
-      <c r="I343" t="s">
-        <v>1118</v>
-      </c>
-      <c r="J343" t="s">
-        <v>1161</v>
       </c>
       <c r="K343" t="s">
         <v>2</v>
@@ -15671,34 +15680,34 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>64301.0</v>
+        <v>63501.0</v>
       </c>
       <c r="B344" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C344" t="s">
         <v>1162</v>
       </c>
-      <c r="C344" t="s">
+      <c r="D344" t="s">
+        <v>35</v>
+      </c>
+      <c r="E344" t="s">
+        <v>35</v>
+      </c>
+      <c r="F344" t="s">
+        <v>124</v>
+      </c>
+      <c r="G344" t="s">
         <v>1163</v>
       </c>
-      <c r="D344" t="s">
-        <v>49</v>
-      </c>
-      <c r="E344" t="s">
-        <v>49</v>
-      </c>
-      <c r="F344" t="s">
-        <v>36</v>
-      </c>
-      <c r="G344" t="s">
+      <c r="H344" t="s">
+        <v>38</v>
+      </c>
+      <c r="I344" t="s">
+        <v>1121</v>
+      </c>
+      <c r="J344" t="s">
         <v>1164</v>
-      </c>
-      <c r="H344" t="s">
-        <v>38</v>
-      </c>
-      <c r="I344" t="s">
-        <v>411</v>
-      </c>
-      <c r="J344" t="s">
-        <v>1165</v>
       </c>
       <c r="K344" t="s">
         <v>2</v>
@@ -15706,34 +15715,34 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>64901.0</v>
+        <v>64301.0</v>
       </c>
       <c r="B345" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C345" t="s">
         <v>1166</v>
       </c>
-      <c r="C345" t="s">
+      <c r="D345" t="s">
+        <v>49</v>
+      </c>
+      <c r="E345" t="s">
+        <v>49</v>
+      </c>
+      <c r="F345" t="s">
+        <v>36</v>
+      </c>
+      <c r="G345" t="s">
         <v>1167</v>
       </c>
-      <c r="D345" t="s">
-        <v>35</v>
-      </c>
-      <c r="E345" t="s">
-        <v>63</v>
-      </c>
-      <c r="F345" t="s">
-        <v>36</v>
-      </c>
-      <c r="G345" t="s">
+      <c r="H345" t="s">
+        <v>38</v>
+      </c>
+      <c r="I345" t="s">
+        <v>411</v>
+      </c>
+      <c r="J345" t="s">
         <v>1168</v>
-      </c>
-      <c r="H345" t="s">
-        <v>38</v>
-      </c>
-      <c r="I345" t="s">
-        <v>1118</v>
-      </c>
-      <c r="J345" t="s">
-        <v>1119</v>
       </c>
       <c r="K345" t="s">
         <v>2</v>
@@ -15741,34 +15750,34 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>67301.0</v>
+        <v>64901.0</v>
       </c>
       <c r="B346" t="s">
         <v>1169</v>
       </c>
       <c r="C346" t="s">
-        <v>1146</v>
+        <v>1170</v>
       </c>
       <c r="D346" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E346" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F346" t="s">
-        <v>1147</v>
+        <v>36</v>
       </c>
       <c r="G346" t="s">
-        <v>1148</v>
+        <v>1171</v>
       </c>
       <c r="H346" t="s">
         <v>38</v>
       </c>
       <c r="I346" t="s">
-        <v>1143</v>
+        <v>1121</v>
       </c>
       <c r="J346" t="s">
-        <v>1144</v>
+        <v>1122</v>
       </c>
       <c r="K346" t="s">
         <v>2</v>
@@ -15776,34 +15785,34 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>63701.0</v>
+        <v>67301.0</v>
       </c>
       <c r="B347" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="C347" t="s">
-        <v>1171</v>
+        <v>1149</v>
       </c>
       <c r="D347" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E347" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="F347" t="s">
-        <v>36</v>
+        <v>1150</v>
       </c>
       <c r="G347" t="s">
-        <v>1172</v>
+        <v>1151</v>
       </c>
       <c r="H347" t="s">
         <v>38</v>
       </c>
       <c r="I347" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="J347" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="K347" t="s">
         <v>2</v>
@@ -15811,7 +15820,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>63301.0</v>
+        <v>63701.0</v>
       </c>
       <c r="B348" t="s">
         <v>1173</v>
@@ -15826,19 +15835,19 @@
         <v>63</v>
       </c>
       <c r="F348" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="G348" t="s">
-        <v>435</v>
+        <v>1175</v>
       </c>
       <c r="H348" t="s">
         <v>38</v>
       </c>
       <c r="I348" t="s">
-        <v>1175</v>
+        <v>1146</v>
       </c>
       <c r="J348" t="s">
-        <v>1176</v>
+        <v>1147</v>
       </c>
       <c r="K348" t="s">
         <v>2</v>
@@ -15846,34 +15855,34 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>68001.0</v>
+        <v>63301.0</v>
       </c>
       <c r="B349" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C349" t="s">
         <v>1177</v>
       </c>
-      <c r="C349" t="s">
-        <v>268</v>
-      </c>
       <c r="D349" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E349" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F349" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G349" t="s">
+        <v>435</v>
+      </c>
+      <c r="H349" t="s">
+        <v>38</v>
+      </c>
+      <c r="I349" t="s">
         <v>1178</v>
       </c>
-      <c r="H349" t="s">
-        <v>38</v>
-      </c>
-      <c r="I349" t="s">
-        <v>1143</v>
-      </c>
       <c r="J349" t="s">
-        <v>1144</v>
+        <v>1179</v>
       </c>
       <c r="K349" t="s">
         <v>2</v>
@@ -15881,34 +15890,34 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>69801.0</v>
+        <v>68001.0</v>
       </c>
       <c r="B350" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="C350" t="s">
-        <v>1180</v>
+        <v>268</v>
       </c>
       <c r="D350" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E350" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F350" t="s">
         <v>36</v>
       </c>
       <c r="G350" t="s">
-        <v>569</v>
+        <v>1181</v>
       </c>
       <c r="H350" t="s">
         <v>38</v>
       </c>
       <c r="I350" t="s">
-        <v>1181</v>
+        <v>1146</v>
       </c>
       <c r="J350" t="s">
-        <v>1182</v>
+        <v>1147</v>
       </c>
       <c r="K350" t="s">
         <v>2</v>
@@ -15916,31 +15925,31 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>52801.0</v>
+        <v>69801.0</v>
       </c>
       <c r="B351" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C351" t="s">
         <v>1183</v>
       </c>
-      <c r="C351" t="s">
-        <v>323</v>
-      </c>
       <c r="D351" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E351" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F351" t="s">
         <v>36</v>
       </c>
       <c r="G351" t="s">
+        <v>569</v>
+      </c>
+      <c r="H351" t="s">
+        <v>38</v>
+      </c>
+      <c r="I351" t="s">
         <v>1184</v>
-      </c>
-      <c r="H351" t="s">
-        <v>38</v>
-      </c>
-      <c r="I351" t="s">
-        <v>143</v>
       </c>
       <c r="J351" t="s">
         <v>1185</v>
@@ -15951,25 +15960,25 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>58201.0</v>
+        <v>52801.0</v>
       </c>
       <c r="B352" t="s">
         <v>1186</v>
       </c>
       <c r="C352" t="s">
+        <v>323</v>
+      </c>
+      <c r="D352" t="s">
+        <v>49</v>
+      </c>
+      <c r="E352" t="s">
+        <v>49</v>
+      </c>
+      <c r="F352" t="s">
+        <v>36</v>
+      </c>
+      <c r="G352" t="s">
         <v>1187</v>
-      </c>
-      <c r="D352" t="s">
-        <v>63</v>
-      </c>
-      <c r="E352" t="s">
-        <v>63</v>
-      </c>
-      <c r="F352" t="s">
-        <v>36</v>
-      </c>
-      <c r="G352" t="s">
-        <v>1188</v>
       </c>
       <c r="H352" t="s">
         <v>38</v>
@@ -15978,7 +15987,7 @@
         <v>143</v>
       </c>
       <c r="J352" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="K352" t="s">
         <v>2</v>
@@ -15986,34 +15995,34 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>56101.0</v>
+        <v>58201.0</v>
       </c>
       <c r="B353" t="s">
-        <v>1091</v>
+        <v>1189</v>
       </c>
       <c r="C353" t="s">
-        <v>1092</v>
+        <v>1190</v>
       </c>
       <c r="D353" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E353" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F353" t="s">
         <v>36</v>
       </c>
       <c r="G353" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="H353" t="s">
         <v>38</v>
       </c>
       <c r="I353" t="s">
-        <v>369</v>
+        <v>143</v>
       </c>
       <c r="J353" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="K353" t="s">
         <v>2</v>
@@ -16021,34 +16030,34 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>55401.0</v>
+        <v>56101.0</v>
       </c>
       <c r="B354" t="s">
-        <v>1191</v>
+        <v>1092</v>
       </c>
       <c r="C354" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D354" t="s">
+        <v>35</v>
+      </c>
+      <c r="E354" t="s">
+        <v>35</v>
+      </c>
+      <c r="F354" t="s">
+        <v>36</v>
+      </c>
+      <c r="G354" t="s">
         <v>1192</v>
       </c>
-      <c r="D354" t="s">
-        <v>63</v>
-      </c>
-      <c r="E354" t="s">
-        <v>63</v>
-      </c>
-      <c r="F354" t="s">
-        <v>36</v>
-      </c>
-      <c r="G354" t="s">
+      <c r="H354" t="s">
+        <v>38</v>
+      </c>
+      <c r="I354" t="s">
+        <v>369</v>
+      </c>
+      <c r="J354" t="s">
         <v>1193</v>
-      </c>
-      <c r="H354" t="s">
-        <v>38</v>
-      </c>
-      <c r="I354" t="s">
-        <v>352</v>
-      </c>
-      <c r="J354" t="s">
-        <v>1194</v>
       </c>
       <c r="K354" t="s">
         <v>2</v>
@@ -16056,25 +16065,25 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>58101.0</v>
+        <v>55401.0</v>
       </c>
       <c r="B355" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C355" t="s">
         <v>1195</v>
       </c>
-      <c r="C355" t="s">
+      <c r="D355" t="s">
+        <v>63</v>
+      </c>
+      <c r="E355" t="s">
+        <v>63</v>
+      </c>
+      <c r="F355" t="s">
+        <v>36</v>
+      </c>
+      <c r="G355" t="s">
         <v>1196</v>
-      </c>
-      <c r="D355" t="s">
-        <v>63</v>
-      </c>
-      <c r="E355" t="s">
-        <v>63</v>
-      </c>
-      <c r="F355" t="s">
-        <v>36</v>
-      </c>
-      <c r="G355" t="s">
-        <v>1197</v>
       </c>
       <c r="H355" t="s">
         <v>38</v>
@@ -16083,7 +16092,7 @@
         <v>352</v>
       </c>
       <c r="J355" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="K355" t="s">
         <v>2</v>
@@ -16091,34 +16100,34 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>56901.0</v>
+        <v>58101.0</v>
       </c>
       <c r="B356" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C356" t="s">
         <v>1199</v>
       </c>
-      <c r="C356" t="s">
+      <c r="D356" t="s">
+        <v>63</v>
+      </c>
+      <c r="E356" t="s">
+        <v>63</v>
+      </c>
+      <c r="F356" t="s">
+        <v>36</v>
+      </c>
+      <c r="G356" t="s">
         <v>1200</v>
       </c>
-      <c r="D356" t="s">
-        <v>63</v>
-      </c>
-      <c r="E356" t="s">
-        <v>63</v>
-      </c>
-      <c r="F356" t="s">
-        <v>36</v>
-      </c>
-      <c r="G356" t="s">
+      <c r="H356" t="s">
+        <v>38</v>
+      </c>
+      <c r="I356" t="s">
+        <v>352</v>
+      </c>
+      <c r="J356" t="s">
         <v>1201</v>
-      </c>
-      <c r="H356" t="s">
-        <v>38</v>
-      </c>
-      <c r="I356" t="s">
-        <v>1202</v>
-      </c>
-      <c r="J356" t="s">
-        <v>1203</v>
       </c>
       <c r="K356" t="s">
         <v>2</v>
@@ -16126,34 +16135,34 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>55301.0</v>
+        <v>56901.0</v>
       </c>
       <c r="B357" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C357" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D357" t="s">
+        <v>63</v>
+      </c>
+      <c r="E357" t="s">
+        <v>63</v>
+      </c>
+      <c r="F357" t="s">
+        <v>36</v>
+      </c>
+      <c r="G357" t="s">
         <v>1204</v>
       </c>
-      <c r="C357" t="s">
+      <c r="H357" t="s">
+        <v>38</v>
+      </c>
+      <c r="I357" t="s">
         <v>1205</v>
       </c>
-      <c r="D357" t="s">
-        <v>35</v>
-      </c>
-      <c r="E357" t="s">
-        <v>35</v>
-      </c>
-      <c r="F357" t="s">
-        <v>36</v>
-      </c>
-      <c r="G357" t="s">
-        <v>397</v>
-      </c>
-      <c r="H357" t="s">
-        <v>38</v>
-      </c>
-      <c r="I357" t="s">
-        <v>107</v>
-      </c>
       <c r="J357" t="s">
-        <v>1069</v>
+        <v>1206</v>
       </c>
       <c r="K357" t="s">
         <v>2</v>
@@ -16161,34 +16170,34 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>54401.0</v>
+        <v>55301.0</v>
       </c>
       <c r="B358" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C358" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="D358" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E358" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F358" t="s">
         <v>36</v>
       </c>
       <c r="G358" t="s">
-        <v>1208</v>
+        <v>397</v>
       </c>
       <c r="H358" t="s">
         <v>38</v>
       </c>
       <c r="I358" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J358" t="s">
-        <v>1209</v>
+        <v>1088</v>
       </c>
       <c r="K358" t="s">
         <v>2</v>
@@ -16196,19 +16205,19 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>57201.0</v>
+        <v>54401.0</v>
       </c>
       <c r="B359" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C359" t="s">
         <v>1210</v>
       </c>
-      <c r="C359" t="s">
-        <v>1104</v>
-      </c>
       <c r="D359" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E359" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F359" t="s">
         <v>36</v>
@@ -16220,7 +16229,7 @@
         <v>38</v>
       </c>
       <c r="I359" t="s">
-        <v>369</v>
+        <v>110</v>
       </c>
       <c r="J359" t="s">
         <v>1212</v>
@@ -16231,34 +16240,34 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>55501.0</v>
+        <v>57201.0</v>
       </c>
       <c r="B360" t="s">
         <v>1213</v>
       </c>
       <c r="C360" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D360" t="s">
+        <v>64</v>
+      </c>
+      <c r="E360" t="s">
+        <v>64</v>
+      </c>
+      <c r="F360" t="s">
+        <v>36</v>
+      </c>
+      <c r="G360" t="s">
         <v>1214</v>
       </c>
-      <c r="D360" t="s">
-        <v>49</v>
-      </c>
-      <c r="E360" t="s">
-        <v>49</v>
-      </c>
-      <c r="F360" t="s">
-        <v>36</v>
-      </c>
-      <c r="G360" t="s">
+      <c r="H360" t="s">
+        <v>38</v>
+      </c>
+      <c r="I360" t="s">
+        <v>369</v>
+      </c>
+      <c r="J360" t="s">
         <v>1215</v>
-      </c>
-      <c r="H360" t="s">
-        <v>38</v>
-      </c>
-      <c r="I360" t="s">
-        <v>112</v>
-      </c>
-      <c r="J360" t="s">
-        <v>1216</v>
       </c>
       <c r="K360" t="s">
         <v>2</v>
@@ -16266,19 +16275,19 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>56501.0</v>
+        <v>55501.0</v>
       </c>
       <c r="B361" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C361" t="s">
         <v>1217</v>
       </c>
-      <c r="C361" t="s">
-        <v>180</v>
-      </c>
       <c r="D361" t="s">
         <v>49</v>
       </c>
       <c r="E361" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F361" t="s">
         <v>36</v>
@@ -16290,10 +16299,10 @@
         <v>38</v>
       </c>
       <c r="I361" t="s">
+        <v>112</v>
+      </c>
+      <c r="J361" t="s">
         <v>1219</v>
-      </c>
-      <c r="J361" t="s">
-        <v>1220</v>
       </c>
       <c r="K361" t="s">
         <v>2</v>
@@ -16301,34 +16310,34 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>60501.0</v>
+        <v>56501.0</v>
       </c>
       <c r="B362" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C362" t="s">
+        <v>180</v>
+      </c>
+      <c r="D362" t="s">
+        <v>49</v>
+      </c>
+      <c r="E362" t="s">
+        <v>64</v>
+      </c>
+      <c r="F362" t="s">
+        <v>36</v>
+      </c>
+      <c r="G362" t="s">
         <v>1221</v>
       </c>
-      <c r="C362" t="s">
+      <c r="H362" t="s">
+        <v>38</v>
+      </c>
+      <c r="I362" t="s">
         <v>1222</v>
       </c>
-      <c r="D362" t="s">
-        <v>63</v>
-      </c>
-      <c r="E362" t="s">
-        <v>63</v>
-      </c>
-      <c r="F362" t="s">
-        <v>36</v>
-      </c>
-      <c r="G362" t="s">
+      <c r="J362" t="s">
         <v>1223</v>
-      </c>
-      <c r="H362" t="s">
-        <v>52</v>
-      </c>
-      <c r="I362" t="s">
-        <v>1224</v>
-      </c>
-      <c r="J362" t="s">
-        <v>54</v>
       </c>
       <c r="K362" t="s">
         <v>2</v>
@@ -16336,34 +16345,34 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>54802.0</v>
+        <v>60501.0</v>
       </c>
       <c r="B363" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C363" t="s">
         <v>1225</v>
       </c>
-      <c r="C363" t="s">
-        <v>869</v>
-      </c>
       <c r="D363" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E363" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F363" t="s">
         <v>36</v>
       </c>
       <c r="G363" t="s">
-        <v>1160</v>
+        <v>1226</v>
       </c>
       <c r="H363" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I363" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="J363" t="s">
-        <v>1227</v>
+        <v>54</v>
       </c>
       <c r="K363" t="s">
         <v>2</v>
@@ -16371,10 +16380,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>54801.0</v>
+        <v>54802.0</v>
       </c>
       <c r="B364" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="C364" t="s">
         <v>869</v>
@@ -16389,16 +16398,16 @@
         <v>36</v>
       </c>
       <c r="G364" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="H364" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I364" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="J364" t="s">
-        <v>54</v>
+        <v>1230</v>
       </c>
       <c r="K364" t="s">
         <v>2</v>
@@ -16406,31 +16415,31 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>60301.0</v>
+        <v>54801.0</v>
       </c>
       <c r="B365" t="s">
         <v>1228</v>
       </c>
       <c r="C365" t="s">
-        <v>1187</v>
+        <v>869</v>
       </c>
       <c r="D365" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E365" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="F365" t="s">
         <v>36</v>
       </c>
       <c r="G365" t="s">
-        <v>1229</v>
+        <v>1163</v>
       </c>
       <c r="H365" t="s">
         <v>52</v>
       </c>
       <c r="I365" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="J365" t="s">
         <v>54</v>
@@ -16441,34 +16450,34 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>57101.0</v>
+        <v>60301.0</v>
       </c>
       <c r="B366" t="s">
         <v>1231</v>
       </c>
       <c r="C366" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D366" t="s">
+        <v>63</v>
+      </c>
+      <c r="E366" t="s">
+        <v>63</v>
+      </c>
+      <c r="F366" t="s">
+        <v>36</v>
+      </c>
+      <c r="G366" t="s">
         <v>1232</v>
       </c>
-      <c r="D366" t="s">
-        <v>35</v>
-      </c>
-      <c r="E366" t="s">
-        <v>35</v>
-      </c>
-      <c r="F366" t="s">
-        <v>36</v>
-      </c>
-      <c r="G366" t="s">
+      <c r="H366" t="s">
+        <v>52</v>
+      </c>
+      <c r="I366" t="s">
         <v>1233</v>
       </c>
-      <c r="H366" t="s">
-        <v>38</v>
-      </c>
-      <c r="I366" t="s">
-        <v>387</v>
-      </c>
       <c r="J366" t="s">
-        <v>1234</v>
+        <v>54</v>
       </c>
       <c r="K366" t="s">
         <v>2</v>
@@ -16476,31 +16485,31 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>61401.0</v>
+        <v>57101.0</v>
       </c>
       <c r="B367" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C367" t="s">
         <v>1235</v>
       </c>
-      <c r="C367" t="s">
+      <c r="D367" t="s">
+        <v>35</v>
+      </c>
+      <c r="E367" t="s">
+        <v>35</v>
+      </c>
+      <c r="F367" t="s">
+        <v>36</v>
+      </c>
+      <c r="G367" t="s">
         <v>1236</v>
       </c>
-      <c r="D367" t="s">
-        <v>49</v>
-      </c>
-      <c r="E367" t="s">
-        <v>49</v>
-      </c>
-      <c r="F367" t="s">
-        <v>36</v>
-      </c>
-      <c r="G367" t="s">
-        <v>1061</v>
-      </c>
       <c r="H367" t="s">
         <v>38</v>
       </c>
       <c r="I367" t="s">
-        <v>1224</v>
+        <v>387</v>
       </c>
       <c r="J367" t="s">
         <v>1237</v>
@@ -16511,7 +16520,7 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>56801.0</v>
+        <v>61401.0</v>
       </c>
       <c r="B368" t="s">
         <v>1238</v>
@@ -16520,25 +16529,25 @@
         <v>1239</v>
       </c>
       <c r="D368" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E368" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F368" t="s">
         <v>36</v>
       </c>
       <c r="G368" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H368" t="s">
+        <v>38</v>
+      </c>
+      <c r="I368" t="s">
+        <v>1227</v>
+      </c>
+      <c r="J368" t="s">
         <v>1240</v>
-      </c>
-      <c r="H368" t="s">
-        <v>38</v>
-      </c>
-      <c r="I368" t="s">
-        <v>1241</v>
-      </c>
-      <c r="J368" t="s">
-        <v>1242</v>
       </c>
       <c r="K368" t="s">
         <v>2</v>
@@ -16546,31 +16555,31 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>57701.0</v>
+        <v>56801.0</v>
       </c>
       <c r="B369" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C369" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D369" t="s">
+        <v>35</v>
+      </c>
+      <c r="E369" t="s">
+        <v>35</v>
+      </c>
+      <c r="F369" t="s">
+        <v>36</v>
+      </c>
+      <c r="G369" t="s">
         <v>1243</v>
       </c>
-      <c r="C369" t="s">
-        <v>942</v>
-      </c>
-      <c r="D369" t="s">
-        <v>49</v>
-      </c>
-      <c r="E369" t="s">
-        <v>49</v>
-      </c>
-      <c r="F369" t="s">
-        <v>36</v>
-      </c>
-      <c r="G369" t="s">
+      <c r="H369" t="s">
+        <v>38</v>
+      </c>
+      <c r="I369" t="s">
         <v>1244</v>
-      </c>
-      <c r="H369" t="s">
-        <v>38</v>
-      </c>
-      <c r="I369" t="s">
-        <v>1241</v>
       </c>
       <c r="J369" t="s">
         <v>1245</v>
@@ -16581,34 +16590,34 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>58901.0</v>
+        <v>57701.0</v>
       </c>
       <c r="B370" t="s">
         <v>1246</v>
       </c>
       <c r="C370" t="s">
+        <v>942</v>
+      </c>
+      <c r="D370" t="s">
+        <v>49</v>
+      </c>
+      <c r="E370" t="s">
+        <v>49</v>
+      </c>
+      <c r="F370" t="s">
+        <v>36</v>
+      </c>
+      <c r="G370" t="s">
         <v>1247</v>
       </c>
-      <c r="D370" t="s">
-        <v>35</v>
-      </c>
-      <c r="E370" t="s">
-        <v>35</v>
-      </c>
-      <c r="F370" t="s">
-        <v>36</v>
-      </c>
-      <c r="G370" t="s">
+      <c r="H370" t="s">
+        <v>38</v>
+      </c>
+      <c r="I370" t="s">
+        <v>1244</v>
+      </c>
+      <c r="J370" t="s">
         <v>1248</v>
-      </c>
-      <c r="H370" t="s">
-        <v>38</v>
-      </c>
-      <c r="I370" t="s">
-        <v>1241</v>
-      </c>
-      <c r="J370" t="s">
-        <v>1249</v>
       </c>
       <c r="K370" t="s">
         <v>2</v>
@@ -16616,34 +16625,34 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>59401.0</v>
+        <v>58901.0</v>
       </c>
       <c r="B371" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C371" t="s">
         <v>1250</v>
       </c>
-      <c r="C371" t="s">
+      <c r="D371" t="s">
+        <v>35</v>
+      </c>
+      <c r="E371" t="s">
+        <v>35</v>
+      </c>
+      <c r="F371" t="s">
+        <v>36</v>
+      </c>
+      <c r="G371" t="s">
         <v>1251</v>
       </c>
-      <c r="D371" t="s">
-        <v>63</v>
-      </c>
-      <c r="E371" t="s">
-        <v>63</v>
-      </c>
-      <c r="F371" t="s">
-        <v>36</v>
-      </c>
-      <c r="G371" t="s">
+      <c r="H371" t="s">
+        <v>38</v>
+      </c>
+      <c r="I371" t="s">
+        <v>1244</v>
+      </c>
+      <c r="J371" t="s">
         <v>1252</v>
-      </c>
-      <c r="H371" t="s">
-        <v>38</v>
-      </c>
-      <c r="I371" t="s">
-        <v>1253</v>
-      </c>
-      <c r="J371" t="s">
-        <v>716</v>
       </c>
       <c r="K371" t="s">
         <v>2</v>
@@ -16651,31 +16660,31 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>59601.0</v>
+        <v>59401.0</v>
       </c>
       <c r="B372" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C372" t="s">
         <v>1254</v>
       </c>
-      <c r="C372" t="s">
-        <v>1251</v>
-      </c>
       <c r="D372" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E372" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F372" t="s">
         <v>36</v>
       </c>
       <c r="G372" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="H372" t="s">
         <v>38</v>
       </c>
       <c r="I372" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="J372" t="s">
         <v>716</v>
@@ -16686,34 +16695,34 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>59501.0</v>
+        <v>59601.0</v>
       </c>
       <c r="B373" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C373" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D373" t="s">
+        <v>35</v>
+      </c>
+      <c r="E373" t="s">
+        <v>35</v>
+      </c>
+      <c r="F373" t="s">
+        <v>36</v>
+      </c>
+      <c r="G373" t="s">
         <v>1255</v>
       </c>
-      <c r="C373" t="s">
+      <c r="H373" t="s">
+        <v>38</v>
+      </c>
+      <c r="I373" t="s">
         <v>1256</v>
       </c>
-      <c r="D373" t="s">
-        <v>49</v>
-      </c>
-      <c r="E373" t="s">
-        <v>64</v>
-      </c>
-      <c r="F373" t="s">
-        <v>36</v>
-      </c>
-      <c r="G373" t="s">
-        <v>1257</v>
-      </c>
-      <c r="H373" t="s">
-        <v>38</v>
-      </c>
-      <c r="I373" t="s">
-        <v>1258</v>
-      </c>
       <c r="J373" t="s">
-        <v>1259</v>
+        <v>716</v>
       </c>
       <c r="K373" t="s">
         <v>2</v>
@@ -16721,16 +16730,16 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>59901.0</v>
+        <v>59501.0</v>
       </c>
       <c r="B374" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="C374" t="s">
-        <v>62</v>
+        <v>1259</v>
       </c>
       <c r="D374" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E374" t="s">
         <v>64</v>
@@ -16739,16 +16748,16 @@
         <v>36</v>
       </c>
       <c r="G374" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H374" t="s">
+        <v>38</v>
+      </c>
+      <c r="I374" t="s">
         <v>1261</v>
       </c>
-      <c r="H374" t="s">
-        <v>38</v>
-      </c>
-      <c r="I374" t="s">
+      <c r="J374" t="s">
         <v>1262</v>
-      </c>
-      <c r="J374" t="s">
-        <v>1263</v>
       </c>
       <c r="K374" t="s">
         <v>2</v>
@@ -16756,34 +16765,34 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>81901.0</v>
+        <v>59901.0</v>
       </c>
       <c r="B375" t="s">
-        <v>890</v>
+        <v>1263</v>
       </c>
       <c r="C375" t="s">
-        <v>865</v>
+        <v>62</v>
       </c>
       <c r="D375" t="s">
         <v>63</v>
       </c>
       <c r="E375" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F375" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="G375" t="s">
-        <v>65</v>
+        <v>1264</v>
       </c>
       <c r="H375" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I375" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="J375" t="s">
-        <v>54</v>
+        <v>1266</v>
       </c>
       <c r="K375" t="s">
         <v>2</v>
@@ -16791,34 +16800,34 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>78901.0</v>
+        <v>81901.0</v>
       </c>
       <c r="B376" t="s">
-        <v>1265</v>
+        <v>890</v>
       </c>
       <c r="C376" t="s">
-        <v>1266</v>
+        <v>865</v>
       </c>
       <c r="D376" t="s">
         <v>63</v>
       </c>
       <c r="E376" t="s">
-        <v>150</v>
+        <v>63</v>
       </c>
       <c r="F376" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G376" t="s">
+        <v>65</v>
+      </c>
+      <c r="H376" t="s">
+        <v>52</v>
+      </c>
+      <c r="I376" t="s">
         <v>1267</v>
       </c>
-      <c r="H376" t="s">
-        <v>38</v>
-      </c>
-      <c r="I376" t="s">
-        <v>1136</v>
-      </c>
       <c r="J376" t="s">
-        <v>785</v>
+        <v>54</v>
       </c>
       <c r="K376" t="s">
         <v>2</v>
@@ -16826,7 +16835,7 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>78401.0</v>
+        <v>78901.0</v>
       </c>
       <c r="B377" t="s">
         <v>1268</v>
@@ -16835,10 +16844,10 @@
         <v>1269</v>
       </c>
       <c r="D377" t="s">
-        <v>533</v>
+        <v>63</v>
       </c>
       <c r="E377" t="s">
-        <v>533</v>
+        <v>150</v>
       </c>
       <c r="F377" t="s">
         <v>36</v>
@@ -16850,10 +16859,10 @@
         <v>38</v>
       </c>
       <c r="I377" t="s">
-        <v>1271</v>
+        <v>1139</v>
       </c>
       <c r="J377" t="s">
-        <v>513</v>
+        <v>785</v>
       </c>
       <c r="K377" t="s">
         <v>2</v>
@@ -16861,19 +16870,19 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>78101.0</v>
+        <v>78401.0</v>
       </c>
       <c r="B378" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C378" t="s">
         <v>1272</v>
       </c>
-      <c r="C378" t="s">
-        <v>1239</v>
-      </c>
       <c r="D378" t="s">
-        <v>35</v>
+        <v>533</v>
       </c>
       <c r="E378" t="s">
-        <v>150</v>
+        <v>533</v>
       </c>
       <c r="F378" t="s">
         <v>36</v>
@@ -16888,7 +16897,7 @@
         <v>1274</v>
       </c>
       <c r="J378" t="s">
-        <v>739</v>
+        <v>513</v>
       </c>
       <c r="K378" t="s">
         <v>2</v>
@@ -16896,34 +16905,34 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>73202.0</v>
+        <v>78101.0</v>
       </c>
       <c r="B379" t="s">
         <v>1275</v>
       </c>
       <c r="C379" t="s">
-        <v>1276</v>
+        <v>1242</v>
       </c>
       <c r="D379" t="s">
         <v>35</v>
       </c>
       <c r="E379" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="F379" t="s">
         <v>36</v>
       </c>
       <c r="G379" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H379" t="s">
+        <v>38</v>
+      </c>
+      <c r="I379" t="s">
         <v>1277</v>
       </c>
-      <c r="H379" t="s">
-        <v>38</v>
-      </c>
-      <c r="I379" t="s">
-        <v>1136</v>
-      </c>
       <c r="J379" t="s">
-        <v>785</v>
+        <v>739</v>
       </c>
       <c r="K379" t="s">
         <v>2</v>
@@ -16931,7 +16940,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>78301.0</v>
+        <v>73202.0</v>
       </c>
       <c r="B380" t="s">
         <v>1278</v>
@@ -16940,10 +16949,10 @@
         <v>1279</v>
       </c>
       <c r="D380" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E380" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="F380" t="s">
         <v>36</v>
@@ -16955,10 +16964,10 @@
         <v>38</v>
       </c>
       <c r="I380" t="s">
-        <v>575</v>
+        <v>1139</v>
       </c>
       <c r="J380" t="s">
-        <v>1281</v>
+        <v>785</v>
       </c>
       <c r="K380" t="s">
         <v>2</v>
@@ -16966,19 +16975,19 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>79101.0</v>
+        <v>78301.0</v>
       </c>
       <c r="B381" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C381" t="s">
         <v>1282</v>
       </c>
-      <c r="C381" t="s">
-        <v>1134</v>
-      </c>
       <c r="D381" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E381" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F381" t="s">
         <v>36</v>
@@ -16990,7 +16999,7 @@
         <v>38</v>
       </c>
       <c r="I381" t="s">
-        <v>1106</v>
+        <v>575</v>
       </c>
       <c r="J381" t="s">
         <v>1284</v>
@@ -17001,16 +17010,16 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>77201.0</v>
+        <v>79101.0</v>
       </c>
       <c r="B382" t="s">
         <v>1285</v>
       </c>
       <c r="C382" t="s">
-        <v>662</v>
+        <v>1137</v>
       </c>
       <c r="D382" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E382" t="s">
         <v>64</v>
@@ -17019,16 +17028,16 @@
         <v>36</v>
       </c>
       <c r="G382" t="s">
-        <v>65</v>
+        <v>1286</v>
       </c>
       <c r="H382" t="s">
         <v>38</v>
       </c>
       <c r="I382" t="s">
-        <v>1234</v>
+        <v>1109</v>
       </c>
       <c r="J382" t="s">
-        <v>796</v>
+        <v>1287</v>
       </c>
       <c r="K382" t="s">
         <v>2</v>
@@ -17036,34 +17045,34 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>77101.0</v>
+        <v>77201.0</v>
       </c>
       <c r="B383" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="C383" t="s">
-        <v>1287</v>
+        <v>662</v>
       </c>
       <c r="D383" t="s">
         <v>50</v>
       </c>
       <c r="E383" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F383" t="s">
         <v>36</v>
       </c>
       <c r="G383" t="s">
-        <v>1288</v>
+        <v>65</v>
       </c>
       <c r="H383" t="s">
         <v>38</v>
       </c>
       <c r="I383" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="J383" t="s">
-        <v>981</v>
+        <v>796</v>
       </c>
       <c r="K383" t="s">
         <v>2</v>
@@ -17071,34 +17080,34 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>78001.0</v>
+        <v>77101.0</v>
       </c>
       <c r="B384" t="s">
         <v>1289</v>
       </c>
       <c r="C384" t="s">
-        <v>571</v>
+        <v>1290</v>
       </c>
       <c r="D384" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E384" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="F384" t="s">
         <v>36</v>
       </c>
       <c r="G384" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H384" t="s">
         <v>38</v>
       </c>
       <c r="I384" t="s">
-        <v>513</v>
+        <v>1237</v>
       </c>
       <c r="J384" t="s">
-        <v>739</v>
+        <v>1064</v>
       </c>
       <c r="K384" t="s">
         <v>2</v>
@@ -17106,34 +17115,34 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>76901.0</v>
+        <v>78001.0</v>
       </c>
       <c r="B385" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="C385" t="s">
-        <v>794</v>
+        <v>571</v>
       </c>
       <c r="D385" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E385" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F385" t="s">
         <v>36</v>
       </c>
       <c r="G385" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H385" t="s">
         <v>38</v>
       </c>
       <c r="I385" t="s">
-        <v>1237</v>
+        <v>513</v>
       </c>
       <c r="J385" t="s">
-        <v>1293</v>
+        <v>739</v>
       </c>
       <c r="K385" t="s">
         <v>2</v>
@@ -17141,19 +17150,19 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>77701.0</v>
+        <v>76901.0</v>
       </c>
       <c r="B386" t="s">
         <v>1294</v>
       </c>
       <c r="C386" t="s">
-        <v>718</v>
+        <v>794</v>
       </c>
       <c r="D386" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E386" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F386" t="s">
         <v>36</v>
@@ -17165,10 +17174,10 @@
         <v>38</v>
       </c>
       <c r="I386" t="s">
+        <v>1240</v>
+      </c>
+      <c r="J386" t="s">
         <v>1296</v>
-      </c>
-      <c r="J386" t="s">
-        <v>895</v>
       </c>
       <c r="K386" t="s">
         <v>2</v>
@@ -17176,34 +17185,34 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>76601.0</v>
+        <v>77701.0</v>
       </c>
       <c r="B387" t="s">
         <v>1297</v>
       </c>
       <c r="C387" t="s">
+        <v>718</v>
+      </c>
+      <c r="D387" t="s">
+        <v>64</v>
+      </c>
+      <c r="E387" t="s">
+        <v>64</v>
+      </c>
+      <c r="F387" t="s">
+        <v>36</v>
+      </c>
+      <c r="G387" t="s">
         <v>1298</v>
       </c>
-      <c r="D387" t="s">
-        <v>49</v>
-      </c>
-      <c r="E387" t="s">
-        <v>49</v>
-      </c>
-      <c r="F387" t="s">
-        <v>124</v>
-      </c>
-      <c r="G387" t="s">
+      <c r="H387" t="s">
+        <v>38</v>
+      </c>
+      <c r="I387" t="s">
         <v>1299</v>
       </c>
-      <c r="H387" t="s">
-        <v>38</v>
-      </c>
-      <c r="I387" t="s">
-        <v>1300</v>
-      </c>
       <c r="J387" t="s">
-        <v>1281</v>
+        <v>895</v>
       </c>
       <c r="K387" t="s">
         <v>2</v>
@@ -17211,22 +17220,22 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>82001.0</v>
+        <v>76601.0</v>
       </c>
       <c r="B388" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C388" t="s">
         <v>1301</v>
       </c>
-      <c r="C388" t="s">
-        <v>1207</v>
-      </c>
       <c r="D388" t="s">
         <v>49</v>
       </c>
       <c r="E388" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F388" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="G388" t="s">
         <v>1302</v>
@@ -17235,10 +17244,10 @@
         <v>38</v>
       </c>
       <c r="I388" t="s">
-        <v>553</v>
+        <v>1303</v>
       </c>
       <c r="J388" t="s">
-        <v>1303</v>
+        <v>1284</v>
       </c>
       <c r="K388" t="s">
         <v>2</v>
@@ -17246,34 +17255,34 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>81801.0</v>
+        <v>82001.0</v>
       </c>
       <c r="B389" t="s">
-        <v>880</v>
+        <v>1304</v>
       </c>
       <c r="C389" t="s">
-        <v>876</v>
+        <v>1210</v>
       </c>
       <c r="D389" t="s">
         <v>49</v>
       </c>
       <c r="E389" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F389" t="s">
         <v>36</v>
       </c>
       <c r="G389" t="s">
-        <v>65</v>
+        <v>1305</v>
       </c>
       <c r="H389" t="s">
         <v>38</v>
       </c>
       <c r="I389" t="s">
-        <v>1165</v>
+        <v>553</v>
       </c>
       <c r="J389" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="K389" t="s">
         <v>2</v>
@@ -17281,34 +17290,34 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>79601.0</v>
+        <v>81801.0</v>
       </c>
       <c r="B390" t="s">
-        <v>1305</v>
+        <v>880</v>
       </c>
       <c r="C390" t="s">
-        <v>1306</v>
+        <v>876</v>
       </c>
       <c r="D390" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E390" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="F390" t="s">
         <v>36</v>
       </c>
       <c r="G390" t="s">
+        <v>65</v>
+      </c>
+      <c r="H390" t="s">
+        <v>38</v>
+      </c>
+      <c r="I390" t="s">
+        <v>1168</v>
+      </c>
+      <c r="J390" t="s">
         <v>1307</v>
-      </c>
-      <c r="H390" t="s">
-        <v>38</v>
-      </c>
-      <c r="I390" t="s">
-        <v>1308</v>
-      </c>
-      <c r="J390" t="s">
-        <v>1309</v>
       </c>
       <c r="K390" t="s">
         <v>2</v>
@@ -17316,34 +17325,34 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>79701.0</v>
+        <v>79601.0</v>
       </c>
       <c r="B391" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C391" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D391" t="s">
+        <v>63</v>
+      </c>
+      <c r="E391" t="s">
+        <v>63</v>
+      </c>
+      <c r="F391" t="s">
+        <v>36</v>
+      </c>
+      <c r="G391" t="s">
         <v>1310</v>
       </c>
-      <c r="C391" t="s">
+      <c r="H391" t="s">
+        <v>38</v>
+      </c>
+      <c r="I391" t="s">
         <v>1311</v>
       </c>
-      <c r="D391" t="s">
-        <v>49</v>
-      </c>
-      <c r="E391" t="s">
-        <v>49</v>
-      </c>
-      <c r="F391" t="s">
-        <v>124</v>
-      </c>
-      <c r="G391" t="s">
+      <c r="J391" t="s">
         <v>1312</v>
-      </c>
-      <c r="H391" t="s">
-        <v>38</v>
-      </c>
-      <c r="I391" t="s">
-        <v>553</v>
-      </c>
-      <c r="J391" t="s">
-        <v>1313</v>
       </c>
       <c r="K391" t="s">
         <v>2</v>
@@ -17351,34 +17360,34 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>80301.0</v>
+        <v>79701.0</v>
       </c>
       <c r="B392" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C392" t="s">
         <v>1314</v>
       </c>
-      <c r="C392" t="s">
+      <c r="D392" t="s">
+        <v>49</v>
+      </c>
+      <c r="E392" t="s">
+        <v>49</v>
+      </c>
+      <c r="F392" t="s">
+        <v>124</v>
+      </c>
+      <c r="G392" t="s">
         <v>1315</v>
       </c>
-      <c r="D392" t="s">
-        <v>49</v>
-      </c>
-      <c r="E392" t="s">
-        <v>49</v>
-      </c>
-      <c r="F392" t="s">
-        <v>36</v>
-      </c>
-      <c r="G392" t="s">
-        <v>1316</v>
-      </c>
       <c r="H392" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I392" t="s">
         <v>553</v>
       </c>
       <c r="J392" t="s">
-        <v>54</v>
+        <v>1316</v>
       </c>
       <c r="K392" t="s">
         <v>2</v>
@@ -17386,34 +17395,34 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>79201.0</v>
+        <v>80301.0</v>
       </c>
       <c r="B393" t="s">
-        <v>920</v>
+        <v>1317</v>
       </c>
       <c r="C393" t="s">
-        <v>921</v>
+        <v>1318</v>
       </c>
       <c r="D393" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E393" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F393" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="G393" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="H393" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I393" t="s">
-        <v>1106</v>
+        <v>553</v>
       </c>
       <c r="J393" t="s">
-        <v>1284</v>
+        <v>54</v>
       </c>
       <c r="K393" t="s">
         <v>2</v>
@@ -17421,22 +17430,22 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>80801.0</v>
+        <v>79201.0</v>
       </c>
       <c r="B394" t="s">
-        <v>1318</v>
+        <v>920</v>
       </c>
       <c r="C394" t="s">
-        <v>1319</v>
+        <v>921</v>
       </c>
       <c r="D394" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E394" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F394" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G394" t="s">
         <v>1320</v>
@@ -17445,10 +17454,10 @@
         <v>38</v>
       </c>
       <c r="I394" t="s">
-        <v>1321</v>
+        <v>1109</v>
       </c>
       <c r="J394" t="s">
-        <v>586</v>
+        <v>1287</v>
       </c>
       <c r="K394" t="s">
         <v>2</v>
@@ -17456,34 +17465,34 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>80201.0</v>
+        <v>80801.0</v>
       </c>
       <c r="B395" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C395" t="s">
         <v>1322</v>
       </c>
-      <c r="C395" t="s">
-        <v>253</v>
-      </c>
       <c r="D395" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E395" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F395" t="s">
         <v>36</v>
       </c>
       <c r="G395" t="s">
-        <v>65</v>
+        <v>1323</v>
       </c>
       <c r="H395" t="s">
         <v>38</v>
       </c>
       <c r="I395" t="s">
-        <v>1119</v>
+        <v>1324</v>
       </c>
       <c r="J395" t="s">
-        <v>1323</v>
+        <v>586</v>
       </c>
       <c r="K395" t="s">
         <v>2</v>
@@ -17491,34 +17500,34 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>81501.0</v>
+        <v>80201.0</v>
       </c>
       <c r="B396" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="C396" t="s">
-        <v>799</v>
+        <v>253</v>
       </c>
       <c r="D396" t="s">
-        <v>800</v>
+        <v>63</v>
       </c>
       <c r="E396" t="s">
-        <v>800</v>
+        <v>64</v>
       </c>
       <c r="F396" t="s">
         <v>36</v>
       </c>
       <c r="G396" t="s">
-        <v>928</v>
+        <v>65</v>
       </c>
       <c r="H396" t="s">
         <v>38</v>
       </c>
       <c r="I396" t="s">
-        <v>1308</v>
+        <v>1122</v>
       </c>
       <c r="J396" t="s">
-        <v>1309</v>
+        <v>1326</v>
       </c>
       <c r="K396" t="s">
         <v>2</v>
@@ -17526,34 +17535,34 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>81001.0</v>
+        <v>81501.0</v>
       </c>
       <c r="B397" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="C397" t="s">
-        <v>1326</v>
+        <v>799</v>
       </c>
       <c r="D397" t="s">
-        <v>63</v>
+        <v>800</v>
       </c>
       <c r="E397" t="s">
-        <v>63</v>
+        <v>800</v>
       </c>
       <c r="F397" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="G397" t="s">
-        <v>1327</v>
+        <v>928</v>
       </c>
       <c r="H397" t="s">
         <v>38</v>
       </c>
       <c r="I397" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="J397" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="K397" t="s">
         <v>2</v>
@@ -17561,7 +17570,7 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>80901.0</v>
+        <v>81001.0</v>
       </c>
       <c r="B398" t="s">
         <v>1328</v>
@@ -17570,13 +17579,13 @@
         <v>1329</v>
       </c>
       <c r="D398" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E398" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F398" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G398" t="s">
         <v>1330</v>
@@ -17585,10 +17594,10 @@
         <v>38</v>
       </c>
       <c r="I398" t="s">
-        <v>1331</v>
+        <v>1311</v>
       </c>
       <c r="J398" t="s">
-        <v>768</v>
+        <v>1312</v>
       </c>
       <c r="K398" t="s">
         <v>2</v>
@@ -17596,19 +17605,19 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>81101.0</v>
+        <v>80901.0</v>
       </c>
       <c r="B399" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C399" t="s">
         <v>1332</v>
       </c>
-      <c r="C399" t="s">
-        <v>1174</v>
-      </c>
       <c r="D399" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E399" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F399" t="s">
         <v>36</v>
@@ -17620,60 +17629,60 @@
         <v>38</v>
       </c>
       <c r="I399" t="s">
-        <v>1308</v>
+        <v>1334</v>
       </c>
       <c r="J399" t="s">
-        <v>1300</v>
+        <v>768</v>
       </c>
       <c r="K399" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="s">
-        <v>1334</v>
+      <c r="A400" t="n">
+        <v>81101.0</v>
       </c>
       <c r="B400" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C400" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D400" t="s">
+        <v>64</v>
+      </c>
+      <c r="E400" t="s">
+        <v>64</v>
+      </c>
+      <c r="F400" t="s">
+        <v>36</v>
+      </c>
+      <c r="G400" t="s">
+        <v>1336</v>
+      </c>
+      <c r="H400" t="s">
+        <v>38</v>
+      </c>
+      <c r="I400" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J400" t="s">
+        <v>1303</v>
+      </c>
+      <c r="K400" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B401" t="s">
         <v>327</v>
       </c>
-      <c r="C400" t="s">
+      <c r="C401" t="s">
         <v>328</v>
       </c>
-      <c r="D400" t="s">
-        <v>63</v>
-      </c>
-      <c r="E400" t="s">
-        <v>63</v>
-      </c>
-      <c r="F400" t="s">
-        <v>36</v>
-      </c>
-      <c r="G400" t="s">
-        <v>1335</v>
-      </c>
-      <c r="H400" t="s">
-        <v>38</v>
-      </c>
-      <c r="I400" t="s">
-        <v>1181</v>
-      </c>
-      <c r="J400" t="s">
-        <v>1181</v>
-      </c>
-      <c r="K400" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="n">
-        <v>70901.0</v>
-      </c>
-      <c r="B401" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C401" t="s">
-        <v>1150</v>
-      </c>
       <c r="D401" t="s">
         <v>63</v>
       </c>
@@ -17684,16 +17693,16 @@
         <v>36</v>
       </c>
       <c r="G401" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H401" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I401" t="s">
-        <v>303</v>
+        <v>1184</v>
       </c>
       <c r="J401" t="s">
-        <v>54</v>
+        <v>1184</v>
       </c>
       <c r="K401" t="s">
         <v>2</v>
@@ -17701,34 +17710,34 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>71701.0</v>
+        <v>70901.0</v>
       </c>
       <c r="B402" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C402" t="s">
-        <v>1339</v>
+        <v>1153</v>
       </c>
       <c r="D402" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E402" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F402" t="s">
         <v>36</v>
       </c>
       <c r="G402" t="s">
-        <v>65</v>
+        <v>1340</v>
       </c>
       <c r="H402" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I402" t="s">
         <v>303</v>
       </c>
       <c r="J402" t="s">
-        <v>884</v>
+        <v>54</v>
       </c>
       <c r="K402" t="s">
         <v>2</v>
@@ -17736,25 +17745,25 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>70601.0</v>
+        <v>71701.0</v>
       </c>
       <c r="B403" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="C403" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="D403" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E403" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F403" t="s">
         <v>36</v>
       </c>
       <c r="G403" t="s">
-        <v>877</v>
+        <v>65</v>
       </c>
       <c r="H403" t="s">
         <v>38</v>
@@ -17771,25 +17780,25 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>71601.0</v>
+        <v>70601.0</v>
       </c>
       <c r="B404" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C404" t="s">
-        <v>104</v>
+        <v>1344</v>
       </c>
       <c r="D404" t="s">
         <v>49</v>
       </c>
       <c r="E404" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F404" t="s">
         <v>36</v>
       </c>
       <c r="G404" t="s">
-        <v>1343</v>
+        <v>877</v>
       </c>
       <c r="H404" t="s">
         <v>38</v>
@@ -17806,34 +17815,34 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>71901.0</v>
+        <v>71601.0</v>
       </c>
       <c r="B405" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="C405" t="s">
-        <v>840</v>
+        <v>104</v>
       </c>
       <c r="D405" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E405" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F405" t="s">
         <v>36</v>
       </c>
       <c r="G405" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H405" t="s">
         <v>38</v>
       </c>
       <c r="I405" t="s">
-        <v>1346</v>
+        <v>303</v>
       </c>
       <c r="J405" t="s">
-        <v>1027</v>
+        <v>884</v>
       </c>
       <c r="K405" t="s">
         <v>2</v>
@@ -17841,13 +17850,13 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>72501.0</v>
+        <v>71901.0</v>
       </c>
       <c r="B406" t="s">
         <v>1347</v>
       </c>
       <c r="C406" t="s">
-        <v>1266</v>
+        <v>840</v>
       </c>
       <c r="D406" t="s">
         <v>63</v>
@@ -17856,7 +17865,7 @@
         <v>63</v>
       </c>
       <c r="F406" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="G406" t="s">
         <v>1348</v>
@@ -17868,7 +17877,7 @@
         <v>1349</v>
       </c>
       <c r="J406" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="K406" t="s">
         <v>2</v>
@@ -17876,34 +17885,34 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>67501.0</v>
+        <v>72501.0</v>
       </c>
       <c r="B407" t="s">
         <v>1350</v>
       </c>
       <c r="C407" t="s">
+        <v>1269</v>
+      </c>
+      <c r="D407" t="s">
+        <v>63</v>
+      </c>
+      <c r="E407" t="s">
+        <v>63</v>
+      </c>
+      <c r="F407" t="s">
+        <v>84</v>
+      </c>
+      <c r="G407" t="s">
         <v>1351</v>
       </c>
-      <c r="D407" t="s">
-        <v>35</v>
-      </c>
-      <c r="E407" t="s">
-        <v>35</v>
-      </c>
-      <c r="F407" t="s">
-        <v>36</v>
-      </c>
-      <c r="G407" t="s">
+      <c r="H407" t="s">
+        <v>38</v>
+      </c>
+      <c r="I407" t="s">
         <v>1352</v>
       </c>
-      <c r="H407" t="s">
-        <v>38</v>
-      </c>
-      <c r="I407" t="s">
-        <v>1353</v>
-      </c>
       <c r="J407" t="s">
-        <v>500</v>
+        <v>1025</v>
       </c>
       <c r="K407" t="s">
         <v>2</v>
@@ -17911,31 +17920,31 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>70101.0</v>
+        <v>67501.0</v>
       </c>
       <c r="B408" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C408" t="s">
         <v>1354</v>
       </c>
-      <c r="C408" t="s">
+      <c r="D408" t="s">
+        <v>35</v>
+      </c>
+      <c r="E408" t="s">
+        <v>35</v>
+      </c>
+      <c r="F408" t="s">
+        <v>36</v>
+      </c>
+      <c r="G408" t="s">
         <v>1355</v>
       </c>
-      <c r="D408" t="s">
-        <v>63</v>
-      </c>
-      <c r="E408" t="s">
-        <v>63</v>
-      </c>
-      <c r="F408" t="s">
-        <v>36</v>
-      </c>
-      <c r="G408" t="s">
+      <c r="H408" t="s">
+        <v>38</v>
+      </c>
+      <c r="I408" t="s">
         <v>1356</v>
-      </c>
-      <c r="H408" t="s">
-        <v>38</v>
-      </c>
-      <c r="I408" t="s">
-        <v>1353</v>
       </c>
       <c r="J408" t="s">
         <v>500</v>
@@ -17946,7 +17955,7 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>67001.0</v>
+        <v>70101.0</v>
       </c>
       <c r="B409" t="s">
         <v>1357</v>
@@ -17955,10 +17964,10 @@
         <v>1358</v>
       </c>
       <c r="D409" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E409" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F409" t="s">
         <v>36</v>
@@ -17970,10 +17979,10 @@
         <v>38</v>
       </c>
       <c r="I409" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="J409" t="s">
-        <v>1361</v>
+        <v>500</v>
       </c>
       <c r="K409" t="s">
         <v>2</v>
@@ -17981,34 +17990,34 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>70301.0</v>
+        <v>67001.0</v>
       </c>
       <c r="B410" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C410" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D410" t="s">
+        <v>35</v>
+      </c>
+      <c r="E410" t="s">
+        <v>35</v>
+      </c>
+      <c r="F410" t="s">
+        <v>36</v>
+      </c>
+      <c r="G410" t="s">
         <v>1362</v>
       </c>
-      <c r="C410" t="s">
+      <c r="H410" t="s">
+        <v>38</v>
+      </c>
+      <c r="I410" t="s">
         <v>1363</v>
       </c>
-      <c r="D410" t="s">
-        <v>49</v>
-      </c>
-      <c r="E410" t="s">
-        <v>49</v>
-      </c>
-      <c r="F410" t="s">
-        <v>36</v>
-      </c>
-      <c r="G410" t="s">
+      <c r="J410" t="s">
         <v>1364</v>
-      </c>
-      <c r="H410" t="s">
-        <v>38</v>
-      </c>
-      <c r="I410" t="s">
-        <v>1365</v>
-      </c>
-      <c r="J410" t="s">
-        <v>500</v>
       </c>
       <c r="K410" t="s">
         <v>2</v>
@@ -18016,31 +18025,31 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>69301.0</v>
+        <v>70301.0</v>
       </c>
       <c r="B411" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C411" t="s">
         <v>1366</v>
       </c>
-      <c r="C411" t="s">
+      <c r="D411" t="s">
+        <v>49</v>
+      </c>
+      <c r="E411" t="s">
+        <v>49</v>
+      </c>
+      <c r="F411" t="s">
+        <v>36</v>
+      </c>
+      <c r="G411" t="s">
         <v>1367</v>
       </c>
-      <c r="D411" t="s">
-        <v>35</v>
-      </c>
-      <c r="E411" t="s">
-        <v>35</v>
-      </c>
-      <c r="F411" t="s">
-        <v>84</v>
-      </c>
-      <c r="G411" t="s">
+      <c r="H411" t="s">
+        <v>38</v>
+      </c>
+      <c r="I411" t="s">
         <v>1368</v>
-      </c>
-      <c r="H411" t="s">
-        <v>38</v>
-      </c>
-      <c r="I411" t="s">
-        <v>1353</v>
       </c>
       <c r="J411" t="s">
         <v>500</v>
@@ -18051,7 +18060,7 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>69701.0</v>
+        <v>69301.0</v>
       </c>
       <c r="B412" t="s">
         <v>1369</v>
@@ -18072,13 +18081,13 @@
         <v>1371</v>
       </c>
       <c r="H412" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I412" t="s">
-        <v>1365</v>
+        <v>1356</v>
       </c>
       <c r="J412" t="s">
-        <v>54</v>
+        <v>500</v>
       </c>
       <c r="K412" t="s">
         <v>2</v>
@@ -18086,31 +18095,31 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>75301.0</v>
+        <v>69701.0</v>
       </c>
       <c r="B413" t="s">
         <v>1372</v>
       </c>
       <c r="C413" t="s">
-        <v>794</v>
+        <v>1373</v>
       </c>
       <c r="D413" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E413" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="F413" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="G413" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H413" t="s">
         <v>52</v>
       </c>
       <c r="I413" t="s">
-        <v>1300</v>
+        <v>1368</v>
       </c>
       <c r="J413" t="s">
         <v>54</v>
@@ -18121,34 +18130,34 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>73901.0</v>
+        <v>75301.0</v>
       </c>
       <c r="B414" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="C414" t="s">
-        <v>1375</v>
+        <v>794</v>
       </c>
       <c r="D414" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E414" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="F414" t="s">
         <v>36</v>
       </c>
       <c r="G414" t="s">
-        <v>397</v>
+        <v>1376</v>
       </c>
       <c r="H414" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I414" t="s">
-        <v>1376</v>
+        <v>1303</v>
       </c>
       <c r="J414" t="s">
-        <v>944</v>
+        <v>54</v>
       </c>
       <c r="K414" t="s">
         <v>2</v>
@@ -18156,34 +18165,34 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>75901.0</v>
+        <v>73901.0</v>
       </c>
       <c r="B415" t="s">
         <v>1377</v>
       </c>
       <c r="C415" t="s">
-        <v>333</v>
+        <v>1378</v>
       </c>
       <c r="D415" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E415" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="F415" t="s">
         <v>36</v>
       </c>
       <c r="G415" t="s">
-        <v>1378</v>
+        <v>397</v>
       </c>
       <c r="H415" t="s">
         <v>38</v>
       </c>
       <c r="I415" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="J415" t="s">
-        <v>739</v>
+        <v>944</v>
       </c>
       <c r="K415" t="s">
         <v>2</v>
@@ -18191,34 +18200,34 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>74301.0</v>
+        <v>75901.0</v>
       </c>
       <c r="B416" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C416" t="s">
+        <v>333</v>
+      </c>
+      <c r="D416" t="s">
+        <v>63</v>
+      </c>
+      <c r="E416" t="s">
+        <v>63</v>
+      </c>
+      <c r="F416" t="s">
+        <v>36</v>
+      </c>
+      <c r="G416" t="s">
+        <v>1381</v>
+      </c>
+      <c r="H416" t="s">
+        <v>38</v>
+      </c>
+      <c r="I416" t="s">
         <v>1379</v>
       </c>
-      <c r="C416" t="s">
-        <v>300</v>
-      </c>
-      <c r="D416" t="s">
-        <v>63</v>
-      </c>
-      <c r="E416" t="s">
-        <v>63</v>
-      </c>
-      <c r="F416" t="s">
-        <v>36</v>
-      </c>
-      <c r="G416" t="s">
-        <v>1380</v>
-      </c>
-      <c r="H416" t="s">
-        <v>38</v>
-      </c>
-      <c r="I416" t="s">
-        <v>1263</v>
-      </c>
       <c r="J416" t="s">
-        <v>1381</v>
+        <v>739</v>
       </c>
       <c r="K416" t="s">
         <v>2</v>
@@ -18226,34 +18235,34 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>60001.0</v>
+        <v>74301.0</v>
       </c>
       <c r="B417" t="s">
         <v>1382</v>
       </c>
       <c r="C417" t="s">
-        <v>1319</v>
+        <v>300</v>
       </c>
       <c r="D417" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E417" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F417" t="s">
-        <v>1147</v>
+        <v>36</v>
       </c>
       <c r="G417" t="s">
-        <v>1320</v>
+        <v>1383</v>
       </c>
       <c r="H417" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I417" t="s">
-        <v>1227</v>
+        <v>1266</v>
       </c>
       <c r="J417" t="s">
-        <v>54</v>
+        <v>1384</v>
       </c>
       <c r="K417" t="s">
         <v>2</v>
@@ -18261,13 +18270,13 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>76501.0</v>
+        <v>60001.0</v>
       </c>
       <c r="B418" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="C418" t="s">
-        <v>1384</v>
+        <v>1322</v>
       </c>
       <c r="D418" t="s">
         <v>49</v>
@@ -18276,19 +18285,19 @@
         <v>49</v>
       </c>
       <c r="F418" t="s">
-        <v>36</v>
+        <v>1150</v>
       </c>
       <c r="G418" t="s">
-        <v>1385</v>
+        <v>1323</v>
       </c>
       <c r="H418" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I418" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="J418" t="s">
-        <v>1386</v>
+        <v>54</v>
       </c>
       <c r="K418" t="s">
         <v>2</v>
@@ -18296,34 +18305,34 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>73201.0</v>
+        <v>76501.0</v>
       </c>
       <c r="B419" t="s">
-        <v>1275</v>
+        <v>1386</v>
       </c>
       <c r="C419" t="s">
-        <v>1276</v>
+        <v>1387</v>
       </c>
       <c r="D419" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E419" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F419" t="s">
         <v>36</v>
       </c>
       <c r="G419" t="s">
-        <v>970</v>
+        <v>1388</v>
       </c>
       <c r="H419" t="s">
         <v>38</v>
       </c>
       <c r="I419" t="s">
-        <v>1387</v>
+        <v>1230</v>
       </c>
       <c r="J419" t="s">
-        <v>720</v>
+        <v>1389</v>
       </c>
       <c r="K419" t="s">
         <v>2</v>
@@ -18331,34 +18340,34 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>73501.0</v>
+        <v>73201.0</v>
       </c>
       <c r="B420" t="s">
-        <v>1388</v>
+        <v>1278</v>
       </c>
       <c r="C420" t="s">
-        <v>1389</v>
+        <v>1279</v>
       </c>
       <c r="D420" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E420" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F420" t="s">
         <v>36</v>
       </c>
       <c r="G420" t="s">
+        <v>980</v>
+      </c>
+      <c r="H420" t="s">
+        <v>38</v>
+      </c>
+      <c r="I420" t="s">
         <v>1390</v>
       </c>
-      <c r="H420" t="s">
-        <v>38</v>
-      </c>
-      <c r="I420" t="s">
-        <v>1391</v>
-      </c>
       <c r="J420" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="K420" t="s">
         <v>2</v>
@@ -18366,34 +18375,34 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>73301.0</v>
+        <v>73501.0</v>
       </c>
       <c r="B421" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C421" t="s">
         <v>1392</v>
       </c>
-      <c r="C421" t="s">
+      <c r="D421" t="s">
+        <v>49</v>
+      </c>
+      <c r="E421" t="s">
+        <v>49</v>
+      </c>
+      <c r="F421" t="s">
+        <v>36</v>
+      </c>
+      <c r="G421" t="s">
         <v>1393</v>
       </c>
-      <c r="D421" t="s">
-        <v>49</v>
-      </c>
-      <c r="E421" t="s">
-        <v>49</v>
-      </c>
-      <c r="F421" t="s">
-        <v>124</v>
-      </c>
-      <c r="G421" t="s">
+      <c r="H421" t="s">
+        <v>38</v>
+      </c>
+      <c r="I421" t="s">
         <v>1394</v>
       </c>
-      <c r="H421" t="s">
-        <v>52</v>
-      </c>
-      <c r="I421" t="s">
-        <v>1387</v>
-      </c>
       <c r="J421" t="s">
-        <v>54</v>
+        <v>711</v>
       </c>
       <c r="K421" t="s">
         <v>2</v>
@@ -18401,34 +18410,34 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>74701.0</v>
+        <v>73301.0</v>
       </c>
       <c r="B422" t="s">
         <v>1395</v>
       </c>
       <c r="C422" t="s">
-        <v>913</v>
+        <v>1396</v>
       </c>
       <c r="D422" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E422" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F422" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="G422" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H422" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I422" t="s">
-        <v>1397</v>
+        <v>1390</v>
       </c>
       <c r="J422" t="s">
-        <v>1398</v>
+        <v>54</v>
       </c>
       <c r="K422" t="s">
         <v>2</v>
@@ -18436,34 +18445,34 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>72701.0</v>
+        <v>74701.0</v>
       </c>
       <c r="B423" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C423" t="s">
+        <v>913</v>
+      </c>
+      <c r="D423" t="s">
+        <v>35</v>
+      </c>
+      <c r="E423" t="s">
+        <v>35</v>
+      </c>
+      <c r="F423" t="s">
+        <v>36</v>
+      </c>
+      <c r="G423" t="s">
         <v>1399</v>
       </c>
-      <c r="C423" t="s">
+      <c r="H423" t="s">
+        <v>38</v>
+      </c>
+      <c r="I423" t="s">
         <v>1400</v>
       </c>
-      <c r="D423" t="s">
-        <v>49</v>
-      </c>
-      <c r="E423" t="s">
-        <v>49</v>
-      </c>
-      <c r="F423" t="s">
-        <v>124</v>
-      </c>
-      <c r="G423" t="s">
+      <c r="J423" t="s">
         <v>1401</v>
-      </c>
-      <c r="H423" t="s">
-        <v>52</v>
-      </c>
-      <c r="I423" t="s">
-        <v>1194</v>
-      </c>
-      <c r="J423" t="s">
-        <v>54</v>
       </c>
       <c r="K423" t="s">
         <v>2</v>
@@ -18471,7 +18480,7 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>71801.0</v>
+        <v>72701.0</v>
       </c>
       <c r="B424" t="s">
         <v>1402</v>
@@ -18486,19 +18495,19 @@
         <v>49</v>
       </c>
       <c r="F424" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="G424" t="s">
         <v>1404</v>
       </c>
       <c r="H424" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I424" t="s">
-        <v>1212</v>
+        <v>1197</v>
       </c>
       <c r="J424" t="s">
-        <v>711</v>
+        <v>54</v>
       </c>
       <c r="K424" t="s">
         <v>2</v>
@@ -18506,7 +18515,7 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>74201.0</v>
+        <v>71801.0</v>
       </c>
       <c r="B425" t="s">
         <v>1405</v>
@@ -18530,29 +18539,64 @@
         <v>38</v>
       </c>
       <c r="I425" t="s">
-        <v>1194</v>
+        <v>1215</v>
       </c>
       <c r="J425" t="s">
+        <v>711</v>
+      </c>
+      <c r="K425" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>74201.0</v>
+      </c>
+      <c r="B426" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C426" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D426" t="s">
+        <v>49</v>
+      </c>
+      <c r="E426" t="s">
+        <v>49</v>
+      </c>
+      <c r="F426" t="s">
+        <v>36</v>
+      </c>
+      <c r="G426" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H426" t="s">
+        <v>38</v>
+      </c>
+      <c r="I426" t="s">
+        <v>1197</v>
+      </c>
+      <c r="J426" t="s">
         <v>684</v>
       </c>
-      <c r="K425" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" s="2" t="s">
-        <v>1408</v>
-      </c>
-      <c r="B428" s="3" t="s">
-        <v>1409</v>
+      <c r="K426" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>1411</v>
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B430" s="3" t="s">
+        <v>1414</v>
       </c>
     </row>
   </sheetData>
